--- a/각종 거시경제지표 해설_v2.xlsx
+++ b/각종 거시경제지표 해설_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daljo\Documents\Desktop\이항섭\260817\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB9257F6-575E-4B63-8490-FE2652EDCDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A164F12-BF54-4F07-8216-74BE00EDA372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22275" yWindow="825" windowWidth="13410" windowHeight="18690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="거시경제지표 해설" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="582">
   <si>
     <t>각종 거시 경제지표 해설</t>
   </si>
@@ -255,1526 +255,1583 @@
     <t>한국 대형주 중심 증시 약세</t>
   </si>
   <si>
+    <t>^KQ11</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/^KQ11</t>
+  </si>
+  <si>
+    <t>중소·벤처·기술주 중심의 코스닥 시장 종합주가지수 — 미국의 나스닥에 대응하는 성격</t>
+  </si>
+  <si>
+    <t>코스피보다 변동성이 크고, 바이오·2차전지·IT 등 성장주 비중이 높아 위험선호(리스크온) 심리에 민감하게 반응하는 경향이 있습니다.</t>
+  </si>
+  <si>
+    <t>성장주·중소형주 중심 위험선호 심리 확대</t>
+  </si>
+  <si>
+    <t>성장주·중소형주 중심 위험회피 심리 확대</t>
+  </si>
+  <si>
+    <t>market_cap</t>
+  </si>
+  <si>
+    <t>KOSIS(국가통계포털)</t>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0029</t>
+  </si>
+  <si>
+    <t>코스피(코스닥 제외) 상장기업 전체의 시가총액 합계</t>
+  </si>
+  <si>
+    <t>KOSIS(국가통계포털) 공식 데이터. S&amp;P500이 미국 대형주 중심 지수이듯, 코스피도 한국 대형주 중심 시장이라 이 둘을 나란히 비교하는 것이 가장 적절한 대응관계입니다.</t>
+  </si>
+  <si>
+    <t>한국 대형주 시장 전체 가치 확대</t>
+  </si>
+  <si>
+    <t>한국 대형주 시장 전체 가치 축소</t>
+  </si>
+  <si>
+    <t>KOSPI PER(일반)</t>
+  </si>
+  <si>
+    <t>per</t>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0033</t>
+  </si>
+  <si>
+    <t>코스피 상장기업 전체의 평균 주가수익비율 — 이익 대비 코스피가 얼마나 비싼지</t>
+  </si>
+  <si>
+    <t>KOSIS(국가통계포털) 공식 데이터. S&amp;P500 PER과 같은 개념으로, 한미 증시의 상대적 밸류에이션을 직접 비교할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>이익 대비 코스피가 비싸지는 국면</t>
+  </si>
+  <si>
+    <t>이익 대비 코스피가 저렴해지는 국면</t>
+  </si>
+  <si>
+    <t>KOSPI PBR</t>
+  </si>
+  <si>
+    <t>pbr</t>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0034</t>
+  </si>
+  <si>
+    <t>코스피 상장기업 전체의 평균 주가순자산비율 — 장부가치 대비 코스피가 얼마나 비싼지</t>
+  </si>
+  <si>
+    <t>KOSIS(국가통계포털) 공식 데이터. 한국 증시는 전통적으로 미국 대비 PBR이 낮게(디스카운트) 형성되는 경향이 있어('코리아 디스카운트' 논의), 이 지표로 그 정도를 추적할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>장부가치 대비 코스피가 비싸지는 국면(디스카운트 축소)</t>
+  </si>
+  <si>
+    <t>장부가치 대비 코스피가 저렴해지는 국면(디스카운트 확대)</t>
+  </si>
+  <si>
+    <t>KOSPI 배당수익률(%)</t>
+  </si>
+  <si>
+    <t>dividend</t>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0032</t>
+  </si>
+  <si>
+    <t>코스피 상장기업 전체의 평균 배당수익률</t>
+  </si>
+  <si>
+    <t>KOSIS(국가통계포털) 공식 데이터. 배당수익률이 국채금리보다 높은지 낮은지는 주식 대비 채권의 상대적 매력을 가늠하는 전통적 잣대 중 하나입니다.</t>
+  </si>
+  <si>
+    <t>배당 매력 확대(주가 하락 또는 배당 확대)</t>
+  </si>
+  <si>
+    <t>배당 매력 축소(주가 상승 또는 배당 축소)</t>
+  </si>
+  <si>
+    <t>해당 원본 지표 기반 자체 계산(추세선 대비 이격도)</t>
+  </si>
+  <si>
+    <t>코스피가 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
+  </si>
+  <si>
+    <t>S&amp;P500 추세이격률과 같은 개념을 코스피에 적용한 지표입니다.</t>
+  </si>
+  <si>
+    <t>양수: 추세선 위(과열 국면 가능성)</t>
+  </si>
+  <si>
+    <t>음수: 추세선 아래(침체 국면 가능성)</t>
+  </si>
+  <si>
+    <t>해당 원본 지표 기반 자체 계산(전월대비 수익률)</t>
+  </si>
+  <si>
+    <t>코스피의 전월 대비 등락률</t>
+  </si>
+  <si>
+    <t>S&amp;P500 월간수익률과 같은 용도로, 한국 증시의 변화율만 따로 비교하고 싶을 때 사용합니다.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>미국 거시지표</t>
+  </si>
+  <si>
+    <t>미국 명목GDP</t>
+  </si>
+  <si>
+    <t>GDP</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/GDP</t>
+  </si>
+  <si>
+    <t>물가상승분을 빼지 않은, 달러로 표시한 미국 경제 전체의 크기</t>
+  </si>
+  <si>
+    <t>실질GDP와 달리 인플레이션 효과가 그대로 포함돼 있어, 실질GDP와 함께 봐야 '진짜 성장'과 '물가상승에 의한 착시'를 구분할 수 있습니다. 버핏지수(시총/GDP)를 계산할 때 분모로도 쓰입니다.</t>
+  </si>
+  <si>
+    <t>경제 규모 확대(다만 물가상승만으로도 오를 수 있어 실질GDP와 함께 확인 필요)</t>
+  </si>
+  <si>
+    <t>디플레이션이나 심각한 경기침체 시에만 드물게 발생</t>
+  </si>
+  <si>
+    <t>미국 CPI</t>
+  </si>
+  <si>
+    <t>CPIAUCSL</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CPIAUCSL</t>
+  </si>
+  <si>
+    <t>소비자가 실제로 구매하는 상품·서비스 가격의 평균적인 변화율(물가상승률)</t>
+  </si>
+  <si>
+    <t>가장 대표적인 인플레이션 측정 지표로, 연준의 금리 결정에 핵심 참고자료로 쓰입니다. 통상 전월비·전년동월비로 인용됩니다.</t>
+  </si>
+  <si>
+    <t>인플레이션 압력 확대, 연준 긴축(금리인상) 가능성 상승 → 통상 주가에 부담</t>
+  </si>
+  <si>
+    <t>인플레이션 완화, 금리인하 기대 상승 → 통상 주가에 우호적</t>
+  </si>
+  <si>
+    <t>미국 실업률</t>
+  </si>
+  <si>
+    <t>UNRATE</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/UNRATE</t>
+  </si>
+  <si>
+    <t>일할 의사가 있는 사람 중 일자리를 구하지 못한 사람의 비율</t>
+  </si>
+  <si>
+    <t>가장 널리 알려진 노동시장 지표지만, 경기가 나빠진 뒤 뒤늦게 반응하는 대표적인 '후행지표'입니다.</t>
+  </si>
+  <si>
+    <t>경기 둔화 신호. 통상 주가에 부정적이나, 연준 금리인하 기대를 자극해 국면에 따라 우호적으로 작용하기도 함</t>
+  </si>
+  <si>
+    <t>고용시장 호조, 경기 개선 신호</t>
+  </si>
+  <si>
+    <t>비농업고용자수</t>
+  </si>
+  <si>
+    <t>PAYEMS</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/PAYEMS</t>
+  </si>
+  <si>
+    <t>농업을 제외한 미국 전체 취업자 수(전월 대비 변화분이 핵심)</t>
+  </si>
+  <si>
+    <t>매월 첫째 주 금요일에 발표되는 '고용보고서'의 핵심 지표로, 시장이 가장 민감하게 반응하는 경제지표 중 하나입니다. 예상치와 크게 어긋나면 주가·금리 변동성이 커집니다.</t>
+  </si>
+  <si>
+    <t>경기 호조 신호. 다만 예상보다 지나치게 강하면 연준 긴축 우려로 이어져 주가에 오히려 부담이 될 수 있음</t>
+  </si>
+  <si>
+    <t>경기 둔화 신호. 통상 주가에 부정적이나, 금리인하 기대를 자극하는 국면에서는 오히려 주가에 우호적으로 해석되기도 함</t>
+  </si>
+  <si>
+    <t>ISM 제조업 PMI</t>
+  </si>
+  <si>
+    <t>ISM/pmi/pm</t>
+  </si>
+  <si>
+    <t>DBnomics(ISM 원자료 재배포, 무료 대안소스)</t>
+  </si>
+  <si>
+    <t>https://db.nomics.world/ISM/pmi/pm</t>
+  </si>
+  <si>
+    <t>제조업 구매관리자들을 설문해 만든 경기 체감 지수(50 기준)</t>
+  </si>
+  <si>
+    <t>50 이상이면 확장, 이하이면 위축 국면을 의미하는 대표적 심리 서베이 지표입니다. FRED의 기존 코드(NAPM)는 2016년 이후 갱신이 중단돼, 무료 대안인 DBnomics 재배포 데이터를 사용합니다. 공식 소스가 아니므로 연동 전 데이터 정합성 검증이 필요합니다.</t>
+  </si>
+  <si>
+    <t>제조업 경기 확장 국면</t>
+  </si>
+  <si>
+    <t>제조업 경기 위축 국면</t>
+  </si>
+  <si>
+    <t>신규 실업급여 신청 건수</t>
+  </si>
+  <si>
+    <t>ICSA</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/ICSA</t>
+  </si>
+  <si>
+    <t>주간</t>
+  </si>
+  <si>
+    <t>한 주 동안 새로 실업급여를 신청한 사람 수</t>
+  </si>
+  <si>
+    <t>매주 목요일 발표되는 고속 노동시장 지표로, 월간 고용지표보다 훨씬 빠르게 경기 변화를 포착합니다. 변동성이 크므로 4주 이동평균과 함께 보는 것이 일반적입니다.</t>
+  </si>
+  <si>
+    <t>고용시장 냉각 신호, 경기둔화 우려 확대</t>
+  </si>
+  <si>
+    <t>고용시장 견조, 경기 호조 신호</t>
+  </si>
+  <si>
+    <t>미국 실질GDP성장률</t>
+  </si>
+  <si>
+    <t>A191RL1Q225SBEA</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/A191RL1Q225SBEA</t>
+  </si>
+  <si>
+    <t>물가상승 효과를 뺀, 미국 경제 전체가 얼마나 빠르게 성장했는지를 보여주는 지표(연율 환산)</t>
+  </si>
+  <si>
+    <t>미국에서 일정 기간 생산된 모든 재화·서비스의 가치를 물가변동 효과를 제거하고 측정한, 경제 전체의 '건강 상태'를 보여주는 가장 포괄적인 지표입니다. 속보치→잠정치→확정치 순으로 한 분기에 세 차례 수정 발표됩니다.</t>
+  </si>
+  <si>
+    <t>경기 확장 국면, 기업이익 개선 기대. 다만 지나치게 높으면 과열·인플레이션 우려로 연준 긴축을 유발할 수 있음</t>
+  </si>
+  <si>
+    <t>경기 둔화·침체 신호. 2분기 연속 마이너스면 통상 '기술적 침체'로 불리나, 미국의 공식 경기침체 판정은 NBER이 별도 기준으로 결정함</t>
+  </si>
+  <si>
+    <t>근원 CPI</t>
+  </si>
+  <si>
+    <t>CPILFESL</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CPILFESL</t>
+  </si>
+  <si>
+    <t>변동성이 큰 식품·에너지 가격을 뺀, 물가의 '기조적인' 흐름</t>
+  </si>
+  <si>
+    <t>일시적인 유가 급등락 같은 노이즈를 제거해 물가의 진짜 추세를 보기 위한 지표입니다. 연준이 일반 CPI보다 더 중요하게 참고하는 경우가 많습니다.</t>
+  </si>
+  <si>
+    <t>CPI와 동일하게 해석하되, 연준의 정책 판단에 더 직접적인 영향을 미침</t>
+  </si>
+  <si>
+    <t>소매 매출액</t>
+  </si>
+  <si>
+    <t>RSAFS</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/RSAFS</t>
+  </si>
+  <si>
+    <t>미국 소비자가 한 달 동안 소매점에서 지출한 총액</t>
+  </si>
+  <si>
+    <t>미국 GDP의 약 2/3를 차지하는 개인소비 중 상품소비 부분을 가장 먼저 보여주는 지표로, 소비 심리와 실제 지출력을 함께 반영합니다.</t>
+  </si>
+  <si>
+    <t>소비 활력 확대, 경기 호조 신호(단 인플레이션에 의한 명목증가 여부 확인 필요)</t>
+  </si>
+  <si>
+    <t>소비 위축, 경기둔화 우려</t>
+  </si>
+  <si>
+    <t>개인소비지출(PCE)</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/PCE</t>
+  </si>
+  <si>
+    <t>미국 가계가 실제로 소비에 지출한 총액(연준이 가장 선호하는 물가지표의 기반)</t>
+  </si>
+  <si>
+    <t>GDP의 소비 항목을 구성하며, 여기서 산출되는 PCE 물가지수는 연준이 CPI보다 더 중시하는 인플레이션 지표입니다.</t>
+  </si>
+  <si>
+    <t>소비 확대, 경기 호조(과열 시 인플레이션 우려)</t>
+  </si>
+  <si>
+    <t>소비 위축, 경기둔화 신호</t>
+  </si>
+  <si>
+    <t>미국 PPI</t>
+  </si>
+  <si>
+    <t>PPIACO</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/PPIACO</t>
+  </si>
+  <si>
+    <t>기업(생산자)이 판매하는 단계에서의 가격 변화 - 소비자물가(CPI)의 '선행지표' 성격</t>
+  </si>
+  <si>
+    <t>원자재-중간재-완제품 단계에서 발생하는 가격 압력을 포착합니다. PPI가 오르면 몇 달 뒤 CPI에도 반영되는 경우가 많아 인플레이션의 조기경보 역할을 합니다.</t>
+  </si>
+  <si>
+    <t>기업 원가 부담 증가 → 마진 압박, 또는 가격전가로 인한 소비자물가 상승 우려</t>
+  </si>
+  <si>
+    <t>원가 부담 완화, 인플레이션 압력 둔화 신호</t>
+  </si>
+  <si>
+    <t>미국 산업생산지수</t>
+  </si>
+  <si>
+    <t>INDPRO</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/INDPRO</t>
+  </si>
+  <si>
+    <t>공장·광산·유틸리티 등 실물 생산활동의 크기를 지수로 나타낸 지표</t>
+  </si>
+  <si>
+    <t>서비스업 비중이 커진 현대 경제에서 예전만큼 비중은 크지 않지만, 여전히 제조업 경기 사이클을 판단하는 핵심 지표로 쓰입니다.</t>
+  </si>
+  <si>
+    <t>제조업 경기 확장, 경기 호조 신호</t>
+  </si>
+  <si>
+    <t>제조업 위축, 경기 둔화 신호. 여러 달 연속 하락하면 경기침체 전조로 해석되기도 함</t>
+  </si>
+  <si>
+    <t>미국 소비자심리지수</t>
+  </si>
+  <si>
+    <t>UMCSENT</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/UMCSENT</t>
+  </si>
+  <si>
+    <t>미시간대 설문조사로 집계하는, 소비자들이 경제를 얼마나 낙관/비관하는지 나타내는 지수</t>
+  </si>
+  <si>
+    <t>실제 소비지출로 이어지기 전 소비자들의 '기대심리'를 미리 포착하는 선행지표 성격을 갖습니다. 미국 GDP의 약 70%가 소비지출이라 중요도가 높습니다.</t>
+  </si>
+  <si>
+    <t>소비 확대 기대, 경기에 우호적</t>
+  </si>
+  <si>
+    <t>소비 위축 우려, 경기 둔화 신호</t>
+  </si>
+  <si>
+    <t>OECD 경기선행지수(미국, CLI)</t>
+  </si>
+  <si>
+    <t>USALOLITONOSTSAM</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/USALOLITONOSTSAM</t>
+  </si>
+  <si>
+    <t>OECD가 여러 선행 지표를 종합해 만든 경기 국면 판단 지수(100 기준)</t>
+  </si>
+  <si>
+    <t>OECD가 직접 산출하며, FRED가 그대로 미러링해 제공하기 때문에 기존 FRED 파이프라인으로 바로 수집 가능합니다. 100을 기준으로 상회/하회 여부와 추세 방향이 핵심입니다.</t>
+  </si>
+  <si>
+    <t>경기 확장 국면 진입 신호</t>
+  </si>
+  <si>
+    <t>경기 둔화·침체 국면 진입 신호</t>
+  </si>
+  <si>
+    <t>개인소득</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/PI</t>
+  </si>
+  <si>
+    <t>미국 가계가 임금, 이자, 배당, 이전소득 등으로 벌어들인 총소득</t>
+  </si>
+  <si>
+    <t>개인소비지출(PCE)과 함께 발표되는 '개인소득 및 지출' 보고서의 핵심 항목으로, 소비 여력의 원천을 보여줍니다.</t>
+  </si>
+  <si>
+    <t>소비 여력 확대 기대</t>
+  </si>
+  <si>
+    <t>소비 위축 가능성</t>
+  </si>
+  <si>
+    <t>내구재 수주</t>
+  </si>
+  <si>
+    <t>DGORDER</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGORDER</t>
+  </si>
+  <si>
+    <t>3년 이상 사용 가능한 내구재(자동차, 기계 등)에 대한 신규 주문 총액</t>
+  </si>
+  <si>
+    <t>기업의 설비투자 의지를 보여주는 선행지표로, 변동성이 큰 항공기 주문을 제외한 '핵심자본재수주'도 함께 참고하는 것이 일반적입니다.</t>
+  </si>
+  <si>
+    <t>기업 투자심리 개선, 향후 생산 확대 기대</t>
+  </si>
+  <si>
+    <t>기업 투자심리 위축, 향후 생산 둔화 우려</t>
+  </si>
+  <si>
+    <t>신규 주택허가 건수</t>
+  </si>
+  <si>
+    <t>PERMIT</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/PERMIT</t>
+  </si>
+  <si>
+    <t>한 달 동안 새로 발급된 신규 주택 건축 허가 건수</t>
+  </si>
+  <si>
+    <t>실제 착공(HOUST)보다 한 단계 앞서 발생하는 절차라 주택시장의 '선행지표' 성격이 더 강합니다.</t>
+  </si>
+  <si>
+    <t>주택시장 활황 기대, 향후 착공 증가 신호</t>
+  </si>
+  <si>
+    <t>주택시장 위축 신호</t>
+  </si>
+  <si>
+    <t>중장비트럭 판매량(선행지표)</t>
+  </si>
+  <si>
+    <t>HTRUCKSSAAR</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/HTRUCKSSAAR</t>
+  </si>
+  <si>
+    <t>물류·건설 등에 쓰이는 대형 트럭의 판매량 - 실물경기의 '선행지표'로 활용되는 지표</t>
+  </si>
+  <si>
+    <t>기업들이 향후 물동량 증가를 예상할 때 미리 트럭을 구매하는 경향이 있어, 공식 경기지표보다 몇 달 앞서 반응하는 경우가 많다고 알려져 있습니다.</t>
+  </si>
+  <si>
+    <t>향후 경기 확장 기대</t>
+  </si>
+  <si>
+    <t>향후 경기 둔화 우려</t>
+  </si>
+  <si>
+    <t>미국 경기침체확률(Chauvet-Piger)</t>
+  </si>
+  <si>
+    <t>RECPROUSM156N</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/RECPROUSM156N</t>
+  </si>
+  <si>
+    <t>여러 경제지표를 통계모델로 종합해 산출한, '지금이 경기침체 국면일 확률'(%)</t>
+  </si>
+  <si>
+    <t>세인트루이스 연준이 제공하는 모델 기반 지표로, 사람의 주관적 판단이 아니라 통계적으로 침체 여부를 추정합니다.</t>
+  </si>
+  <si>
+    <t>침체 가능성 확대(통상 50%를 넘으면 침체 국면 진입 가능성이 높다고 해석)</t>
+  </si>
+  <si>
+    <t>침체 가능성 낮음, 경기 안정적</t>
+  </si>
+  <si>
+    <t>금리·통화</t>
+  </si>
+  <si>
+    <t>미국 10년 국채금리</t>
+  </si>
+  <si>
+    <t>DGS10</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGS10</t>
+  </si>
+  <si>
+    <t>만기 10년짜리 미국 국채에 적용되는 시장금리 - 주식 밸류에이션의 할인율, 모기지 금리의 기준으로 쓰이는 '만능 기준금리'</t>
+  </si>
+  <si>
+    <t>국채금리는 만기가 길수록 통상 더 높은 것이 정상입니다(장기 투자 리스크 프리미엄). 10년물은 전 세계 자산가격에 가장 폭넓은 영향을 미치는 금리입니다.</t>
+  </si>
+  <si>
+    <t>대출비용 상승, 채권가격 하락, 성장주 밸류에이션 부담</t>
+  </si>
+  <si>
+    <t>대출비용 하락, 채권가격 상승, 밸류에이션 부담 완화</t>
+  </si>
+  <si>
+    <t>미국 기준금리(FFR, 실효금리)</t>
+  </si>
+  <si>
+    <t>FEDFUNDS</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
+  </si>
+  <si>
+    <t>은행 간 초단기 자금 거래에 적용되는 금리 - 연준 통화정책의 핵심 수단</t>
+  </si>
+  <si>
+    <t>연준이 직접 통제하는 정책금리로, 대출·예금·채권 등 다른 모든 금리의 기준점 역할을 합니다. FOMC 회의에서 목표 범위를 정하고, 실효금리는 그 범위 안에서 실제 거래된 평균금리입니다.</t>
+  </si>
+  <si>
+    <t>긴축 국면, 대출비용 증가 → 통상 주가에 부담</t>
+  </si>
+  <si>
+    <t>완화 국면, 대출비용 감소 → 통상 주가에 우호적</t>
+  </si>
+  <si>
+    <t>미국 2Y-10Y 금리차</t>
+  </si>
+  <si>
+    <t>T10Y2Y</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/T10Y2Y</t>
+  </si>
+  <si>
+    <t>10년물 금리에서 2년물 금리를 뺀 값 - 장단기 금리차(수익률곡선의 기울기)</t>
+  </si>
+  <si>
+    <t>정상적인 경우 장기금리가 단기금리보다 높아 이 값은 양수입니다. 이 값이 음수로 뒤집히는 '역전' 현상은 역사적으로 경기침체를 앞서 예고해온 대표적 선행지표입니다.</t>
+  </si>
+  <si>
+    <t>정상 상태(플러스). 역전 이후 정상화되는 시점이 오히려 침체 시작과 겹치는 경우도 있어 해석에 주의가 필요함</t>
+  </si>
+  <si>
+    <t>역전(마이너스): 경기침체 경고 신호. 다만 실제 침체까지 통상 12~24개월의 시차가 있어 즉각적인 신호는 아님</t>
+  </si>
+  <si>
+    <t>달러인덱스(DXY)</t>
+  </si>
+  <si>
+    <t>DX-Y.NYB</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/DX-Y.NYB</t>
+  </si>
+  <si>
+    <t>유로, 엔, 파운드 등 주요 6개 통화 대비 달러의 종합적인 강세/약세를 나타내는 지수</t>
+  </si>
+  <si>
+    <t>특정 한 통화쌍이 아니라 '달러 전체의 힘'을 보여줍니다. 달러 강세는 신흥국 자금 이탈, 원자재 가격 하락, 미국 다국적기업의 해외실적 환산 감소로 이어지는 경우가 많습니다.</t>
+  </si>
+  <si>
+    <t>달러 강세: 신흥국·원자재·미국 다국적기업 해외실적에 부담</t>
+  </si>
+  <si>
+    <t>달러 약세: 신흥국·원자재·미국 다국적기업 해외실적에 우호적</t>
+  </si>
+  <si>
+    <t>미국 기준금리(목표, 계단식)</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>FRED(DFEDTAR+DFEDTARU 결합), 자체 계산</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DFEDTARU</t>
+  </si>
+  <si>
+    <t>연준이 FOMC에서 설정하는 기준금리 목표 범위(상단·하단을 상단값으로 계단식 통합)</t>
+  </si>
+  <si>
+    <t>연준은 2008년 12월 이전엔 단일 숫자로, 이후엔 범위(예: 5.25~5.50%)로 기준금리를 발표합니다. 이 지표는 2008년 이전 단일목표(DFEDTAR)와 이후 범위의 상단(DFEDTARU)을 하나로 이어붙여, 전체 역사를 계단식 그래프 하나로 볼 수 있게 만든 것입니다. 실효금리(FEDFUNDS)는 이 범위 안에서 실제 거래된 값이라 소폭 다르게 움직일 수 있습니다.</t>
+  </si>
+  <si>
+    <t>긴축(금리인상) 국면 — 대출비용 상승, 유동성 축소로 통상 주식·채권 등 위험자산에 부담</t>
+  </si>
+  <si>
+    <t>완화(금리인하) 국면 — 대출비용 하락, 유동성 확대로 통상 위험자산에 우호적</t>
+  </si>
+  <si>
+    <t>미국 M2 통화량</t>
+  </si>
+  <si>
+    <t>M2SL</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/M2SL</t>
+  </si>
+  <si>
+    <t>현금+예금+단기금융상품을 합친, 시중에 풀린 돈의 총량</t>
+  </si>
+  <si>
+    <t>통화량이 늘면 이론적으로 자산시장에 유입될 유동성이 늘어난다고 해석됩니다. 다만 실제 주가와의 관계는 시차가 있고 국면에 따라 불안정한 경우가 많습니다.</t>
+  </si>
+  <si>
+    <t>유동성 확대, 자산가격에 우호적일 수 있음</t>
+  </si>
+  <si>
+    <t>유동성 축소(드문 현상), 자산가격에 부담 요인</t>
+  </si>
+  <si>
+    <t>연준 자산규모(Fed B/S)</t>
+  </si>
+  <si>
+    <t>WALCL</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/WALCL</t>
+  </si>
+  <si>
+    <t>연준이 보유한 국채·MBS 등 자산의 총 규모 - 양적완화(QE)/양적긴축(QT) 여부를 보여주는 지표</t>
+  </si>
+  <si>
+    <t>연준이 채권을 사들이면(QE) 이 수치가 늘고 시중에 돈이 풀립니다. 반대로 팔거나 만기상환을 방치하면(QT) 줄어듭니다. 2020년 팬데믹 QE, 2022년 이후 QT가 대표적 사례입니다.</t>
+  </si>
+  <si>
+    <t>확대(QE): 유동성 공급, 통상 위험자산 가격에 우호적</t>
+  </si>
+  <si>
+    <t>축소(QT): 유동성 회수, 통상 위험자산 가격에 부담</t>
+  </si>
+  <si>
+    <t>미국 30년 모기지금리</t>
+  </si>
+  <si>
+    <t>MORTGAGE30US</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/MORTGAGE30US</t>
+  </si>
+  <si>
+    <t>미국 주택담보대출(30년 고정금리)의 평균 금리</t>
+  </si>
+  <si>
+    <t>미국 주택시장의 활황/침체를 가르는 핵심 변수입니다. 10년 국채금리에 연동되어 움직이는 경향이 있습니다.</t>
+  </si>
+  <si>
+    <t>주택구매 부담 증가, 주택경기 위축 우려</t>
+  </si>
+  <si>
+    <t>주택구매 부담 완화, 주택경기 개선 기대</t>
+  </si>
+  <si>
+    <t>미국 3개월 국채금리</t>
+  </si>
+  <si>
+    <t>DGS3MO</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGS3MO</t>
+  </si>
+  <si>
+    <t>만기 3개월짜리 미국 국채에 적용되는 시장금리 - 연준 정책금리에 가장 민감하게 반응하는 단기금리</t>
+  </si>
+  <si>
+    <t>장단기 금리차를 계산할 때 10년물과 짝지어 자주 쓰이며, 연준 정책 변화를 가장 빠르게 반영하는 금리입니다.</t>
+  </si>
+  <si>
+    <t>단기 자금조달 비용 상승</t>
+  </si>
+  <si>
+    <t>단기 자금조달 비용 하락</t>
+  </si>
+  <si>
+    <t>미국 2년 국채금리</t>
+  </si>
+  <si>
+    <t>DGS2</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGS2</t>
+  </si>
+  <si>
+    <t>만기 2년짜리 미국 국채에 적용되는 시장금리 - 향후 1~2년 연준 정책 경로에 대한 시장의 기대를 반영</t>
+  </si>
+  <si>
+    <t>10년물과의 금리차(2Y-10Y)가 경기침체 예측 지표로 널리 활용됩니다.</t>
+  </si>
+  <si>
+    <t>향후 긴축 기대 강화</t>
+  </si>
+  <si>
+    <t>향후 완화(금리인하) 기대 강화</t>
+  </si>
+  <si>
+    <t>엔/달러 환율</t>
+  </si>
+  <si>
+    <t>DEXJPUS</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DEXJPUS</t>
+  </si>
+  <si>
+    <t>1달러를 사는 데 필요한 엔화의 양</t>
+  </si>
+  <si>
+    <t>일본은행의 통화정책, 글로벌 '엔캐리 트레이드'(저금리 엔화를 빌려 다른 자산에 투자) 자금 흐름과 밀접하게 연동됩니다.</t>
+  </si>
+  <si>
+    <t>엔화 약세: 일본 수출기업에 유리, 엔캐리 트레이드 확대 유인</t>
+  </si>
+  <si>
+    <t>엔화 강세: 엔캐리 트레이드 청산 압력(글로벌 자산시장 변동성 확대 요인이 되기도 함)</t>
+  </si>
+  <si>
+    <t>지수·주가</t>
+  </si>
+  <si>
+    <t>S&amp;P500</t>
+  </si>
+  <si>
+    <t>^GSPC</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/^GSPC</t>
+  </si>
+  <si>
+    <t>미국 대형주 약 500개로 구성된, 미국 증시 전체를 대표하는 가장 널리 쓰이는 벤치마크 지수</t>
+  </si>
+  <si>
+    <t>시가총액 가중 방식으로 산출되어, 애플·마이크로소프트 등 초대형주의 영향력이 특히 큽니다.</t>
+  </si>
+  <si>
+    <t>나스닥100</t>
+  </si>
+  <si>
+    <t>^NDX</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/^NDX</t>
+  </si>
+  <si>
+    <t>나스닥 상장 비금융 대형주 100개로 구성된, 기술주 비중이 매우 높은 지수</t>
+  </si>
+  <si>
+    <t>성장주·기술주 성격이 강해 금리, 달러 변동에 S&amp;P500보다 더 민감하게 반응하는 경향이 있습니다.</t>
+  </si>
+  <si>
+    <t>다우존스</t>
+  </si>
+  <si>
+    <t>^DJI</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/^DJI</t>
+  </si>
+  <si>
+    <t>미국 우량 대형주 30개로 구성된, 가장 오래된 미국 주가지수</t>
+  </si>
+  <si>
+    <t>종목 수가 적고 가격가중 방식이라 S&amp;P500보다 대표성은 떨어지지만, 역사가 길어 여전히 널리 인용됩니다.</t>
+  </si>
+  <si>
+    <t>니케이225(일본)</t>
+  </si>
+  <si>
+    <t>^N225</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/^N225</t>
+  </si>
+  <si>
+    <t>일본 대표 기업 225개로 구성된 일본 증시 대표 지수</t>
+  </si>
+  <si>
+    <t>엔화 약세 국면에서 수출기업 실적 개선 기대로 상승하는 경향이 있어, 엔/달러 환율과 자주 함께 비교됩니다.</t>
+  </si>
+  <si>
+    <t>미국 전체 시가총액(조달러)</t>
+  </si>
+  <si>
+    <t>FRED(연준 Z.1 자금순환통계)</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BOGZ1LM893064105Q</t>
+  </si>
+  <si>
+    <t>미국 상장기업 전체의 시가총액 합계(연준 공식 집계, 조 달러 단위)</t>
+  </si>
+  <si>
+    <t>연준 Z.1 자금순환 통계(BOGZ1LM893064105Q)가 분기마다 집계하는, 미국 전체 상장기업 주식의 시가총액입니다. 버핏지수(시총/GDP)를 계산할 때 쓰는 분자와 동일한 원본 데이터이며, S&amp;P500 같은 개별 지수와 달리 신규상장·상장폐지·자사주매입 등 시장 전체의 물량 변화까지 반영합니다. 분기 발표라 일간 지수들과 달리 계단식으로 표시됩니다.</t>
+  </si>
+  <si>
+    <t>미국 주식시장 전체 가치 확대 — 경기 호조 또는 밸류에이션 확장을 반영</t>
+  </si>
+  <si>
+    <t>미국 주식시장 전체 가치 축소 — 경기 둔화 또는 밸류에이션 위축을 반영</t>
+  </si>
+  <si>
+    <t>VIX(변동성지수)</t>
+  </si>
+  <si>
+    <t>VIXCLS</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
+  </si>
+  <si>
+    <t>S&amp;P500 옵션 가격에서 역산한, 앞으로 30일간 예상되는 변동성 - 일명 '공포지수'</t>
+  </si>
+  <si>
+    <t>시장 참여자들이 얼마나 큰 가격 변동을 예상하는지를 보여주는 지표로, S&amp;P500 옵션의 내재변동성으로 산출되어 주가와 구조적으로 강한 음의 상관을 가집니다.</t>
+  </si>
+  <si>
+    <t>시장 불안·공포 확산, 통상 주가 하락과 동행</t>
+  </si>
+  <si>
+    <t>시장 안정·낙관, 통상 주가 상승과 동행</t>
+  </si>
+  <si>
+    <t>CBOE 풋/콜비율(주식)</t>
+  </si>
+  <si>
+    <t>equity</t>
+  </si>
+  <si>
+    <t>CBOE(공개 CSV, 2019.10 이후 갱신중단)</t>
+  </si>
+  <si>
+    <t>https://www.cboe.com/us/options/market_statistics/daily/</t>
+  </si>
+  <si>
+    <t>풋옵션(하락 베팅) 거래량을 콜옵션(상승 베팅) 거래량으로 나눈 비율</t>
+  </si>
+  <si>
+    <t>투자자들의 방향성 심리를 보여주는 지표입니다. 다만 단순 선형관계보다 '역발상(contrarian)' 지표로 활용됩니다.</t>
+  </si>
+  <si>
+    <t>비율이 극단적으로 낮음(다들 상승 베팅): 낙관 과잉, 고점 경계 신호로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>비율이 극단적으로 높음(다들 하락 베팅): 비관 과잉, 저점 근접 신호로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>신용·부채</t>
+  </si>
+  <si>
+    <t>하이일드 스프레드(HY OAS, CDS프록시)</t>
+  </si>
+  <si>
+    <t>BAMLH0A0HYM2</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BAMLH0A0HYM2</t>
+  </si>
+  <si>
+    <t>신용등급이 낮은 회사채(정크본드) 금리가 안전한 국채금리보다 얼마나 더 높은지를 나타내는 '위험 프리미엄'</t>
+  </si>
+  <si>
+    <t>스프레드가 벌어질수록 투자자들이 신용위험을 더 크게 우려한다는 뜻입니다. 경기침체·금융위기 국면(2008, 2020, 2022년)에서 급등하는 경향을 보였습니다.</t>
+  </si>
+  <si>
+    <t>스프레드 확대: 신용경색, 위험회피 심리 확산, 통상 주가에 부담</t>
+  </si>
+  <si>
+    <t>스프레드 축소: 신용시장 안정, 위험선호 심리 확산, 통상 주가에 우호적</t>
+  </si>
+  <si>
+    <t>마진부채(FINRA, YoY%)</t>
+  </si>
+  <si>
+    <t>yoy</t>
+  </si>
+  <si>
+    <t>FINRA(공개 엑셀)</t>
+  </si>
+  <si>
+    <t>https://www.finra.org/investors/learn-to-invest/advanced-investing/margin-statistics</t>
+  </si>
+  <si>
+    <t>마진부채 잔액의 전년동월대비 증가율</t>
+  </si>
+  <si>
+    <t>절대 잔액보다 '변화 속도'를 보는 지표로, 나스닥100 등 성장주와 함께 움직이는 경향이 있다고 알려져 있습니다.</t>
+  </si>
+  <si>
+    <t>레버리지 증가 속도 가속, 투자심리 과열 가능성</t>
+  </si>
+  <si>
+    <t>레버리지 증가 속도 둔화 또는 감소, 위험회피 심리 확산</t>
+  </si>
+  <si>
+    <t>투자등급 스프레드(IG OAS)</t>
+  </si>
+  <si>
+    <t>BAMLC0A0CM</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BAMLC0A0CM</t>
+  </si>
+  <si>
+    <t>우량 회사채(투자등급)와 국채 간 금리차 - 하이일드보다 안정적인 신용시장 온도계</t>
+  </si>
+  <si>
+    <t>하이일드 스프레드보다 변동성은 작지만 같은 방향으로 움직이며, 우량기업의 자금조달 여건을 보여줍니다.</t>
+  </si>
+  <si>
+    <t>스프레드 확대: 신용여건 악화(강도는 하이일드보다 약함)</t>
+  </si>
+  <si>
+    <t>스프레드 축소: 신용여건 개선(강도는 하이일드보다 약함)</t>
+  </si>
+  <si>
+    <t>마진부채(FINRA, 잔액)</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>투자자들이 증권사에서 빌려서 주식을 산 금액(레버리지 투자 규모)의 잔액</t>
+  </si>
+  <si>
+    <t>마진부채가 늘면 투자자들의 위험선호(레버리지 사용)가 커졌다는 뜻입니다. 반대로 주가 급락 시 마진콜(추가담보 요구)로 강제매도가 발생해 하락을 증폭시키는 '레버리지 청산' 리스크의 원천이 되기도 합니다.</t>
+  </si>
+  <si>
+    <t>레버리지 확대, 투자심리 과열 가능성(특히 사상최고치 경신 시 경계 신호로 해석되기도 함)</t>
+  </si>
+  <si>
+    <t>레버리지 축소, 급격한 하락은 강제청산(디레버리징) 진행 중일 가능성</t>
+  </si>
+  <si>
+    <t>미국 가계부채</t>
+  </si>
+  <si>
+    <t>CMDEBT</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CMDEBT</t>
+  </si>
+  <si>
+    <t>미국 가계 전체가 지고 있는 빚(주택담보대출, 신용카드 등)의 총액</t>
+  </si>
+  <si>
+    <t>가계부채가 소득 대비 과도하게 늘어나면 소비여력 축소, 금융위기 리스크로 이어질 수 있습니다(2008년 금융위기가 대표적 사례).</t>
+  </si>
+  <si>
+    <t>레버리지 확대, 장기적으로 소비여력·금융안정성에 부담 우려</t>
+  </si>
+  <si>
+    <t>디레버리징(부채 축소) 진행 중</t>
+  </si>
+  <si>
+    <t>미국 정부부채(총액)</t>
+  </si>
+  <si>
+    <t>GFDEBTN</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/GFDEBTN</t>
+  </si>
+  <si>
+    <t>미국 연방정부가 누적으로 지고 있는 빚의 총액</t>
+  </si>
+  <si>
+    <t>재정건전성과 장기 금리·인플레이션 우려에 영향을 줄 수 있는 구조적 지표입니다. 단기 주가 변동과의 직접적 상관은 약한 편입니다.</t>
+  </si>
+  <si>
+    <t>재정 부담 증가, 장기적으로 금리·인플레이션 상방 압력 우려</t>
+  </si>
+  <si>
+    <t>해당 없음(구조적으로 꾸준히 증가하는 지표라 감소는 매우 드묾)</t>
+  </si>
+  <si>
+    <t>외환·무역</t>
+  </si>
+  <si>
+    <t>미국 무역수지</t>
+  </si>
+  <si>
+    <t>BOPGSTB</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BOPGSTB</t>
+  </si>
+  <si>
+    <t>상품·서비스 수출액에서 수입액을 뺀 값(경상수지보다 좁은 개념)</t>
+  </si>
+  <si>
+    <t>무역정책, 관세 이슈 등에 민감하게 반응하며 매월 발표되어 경상수지보다 시장의 관심을 자주 받습니다.</t>
+  </si>
+  <si>
+    <t>적자 축소(또는 흑자 확대): 대외 경쟁력 개선 신호</t>
+  </si>
+  <si>
+    <t>적자 확대: 대외 경쟁력 약화 또는 내수 수요 강세 신호</t>
+  </si>
+  <si>
+    <t>미국 경상수지</t>
+  </si>
+  <si>
+    <t>IEABC</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/IEABC</t>
+  </si>
+  <si>
+    <t>상품·서비스·소득 등을 종합한 미국의 대외 거래 결과(적자/흑자)</t>
+  </si>
+  <si>
+    <t>미국은 구조적으로 경상수지 적자국입니다. 적자 확대는 달러 공급 증가로 이어져 장기적으로 달러 약세 요인이 될 수 있습니다.</t>
+  </si>
+  <si>
+    <t>적자 축소(또는 흑자 확대): 장기적으로 달러 강세 요인</t>
+  </si>
+  <si>
+    <t>적자 확대: 장기적으로 달러 약세 요인</t>
+  </si>
+  <si>
+    <t>원자재</t>
+  </si>
+  <si>
+    <t>WTI 원유</t>
+  </si>
+  <si>
+    <t>DCOILWTICO</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DCOILWTICO</t>
+  </si>
+  <si>
+    <t>미국산 원유의 대표 기준 가격</t>
+  </si>
+  <si>
+    <t>에너지비용, 인플레이션, 산유국 경기에 광범위한 영향을 미칩니다. 수요 견인형 상승은 경기 호조 반영, 공급 충격형 상승(전쟁·감산 등)은 인플레이션·소비위축 우려로 작용하는 등 원인에 따라 해석이 달라집니다.</t>
+  </si>
+  <si>
+    <t>수요 견인형: 경기 호조 반영, 주가에 우호적일 수 있음 / 공급 충격형: 인플레이션·소비위축 우려, 주가에 부담</t>
+  </si>
+  <si>
+    <t>수요 위축(경기 둔화 우려) 또는 공급 과잉을 반영</t>
+  </si>
+  <si>
+    <t>금 선물</t>
+  </si>
+  <si>
+    <t>GC=F</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/GC=F</t>
+  </si>
+  <si>
+    <t>대표적인 안전자산이자 인플레이션 헤지 수단으로 여겨지는 금의 선물 가격</t>
+  </si>
+  <si>
+    <t>통상 금리(특히 실질금리)가 낮을수록, 지정학적·경제적 불확실성이 커질수록 매력이 높아지는 경향이 있습니다. 달러와는 대체로 반대 방향으로 움직입니다.</t>
+  </si>
+  <si>
+    <t>안전자산 선호 확대(불확실성 고조, 금리 하락, 달러 약세 국면)</t>
+  </si>
+  <si>
+    <t>위험자산 선호 확대(안정적 성장, 금리 상승, 달러 강세 국면)</t>
+  </si>
+  <si>
+    <t>은 선물</t>
+  </si>
+  <si>
+    <t>SI=F</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/SI=F</t>
+  </si>
+  <si>
+    <t>금과 유사한 안전자산 성격이지만, 전자·태양광 등 산업용 수요 비중이 높아 경기 민감도가 더 큰 귀금속</t>
+  </si>
+  <si>
+    <t>금보다 변동성이 크고, '안전자산' 성격과 '산업재' 성격이 혼재되어 있어 해석이 금보다 복잡합니다.</t>
+  </si>
+  <si>
+    <t>안전자산 수요 또는 산업용 수요(태양광 등 친환경 산업 확대) 증가</t>
+  </si>
+  <si>
+    <t>안전자산 수요 위축 또는 산업 경기 둔화</t>
+  </si>
+  <si>
+    <t>발틱운임지수(BDI) 프록시-건화물운임선물ETF</t>
+  </si>
+  <si>
+    <t>BDRY</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/quote/BDRY</t>
+  </si>
+  <si>
+    <t>벌크선 운임선물에 직접 투자하는 ETF(BDRY) 가격 — 발틱운임지수(BDI)와 가장 밀접하게 연동되는 무료 대안</t>
+  </si>
+  <si>
+    <t>발틱운임지수(BDI) 자체는 Baltic Exchange의 유료 데이터로만 제공되며 무료 API가 없습니다. 초기엔 해운주 ETF(SEA)를 프록시로 검토했으나, 이 ETF는 2022년경 펀드가 재편되며 그 이전 이력이 사라졌고 해운'주식'을 담아 BDI와 간접적 관계였습니다. 이후 Capesize·Panamax·Supramax 건화물 운임선물을 직접 편입하는 BDRY(2018년 3월 상장)로 교체해, BDI 실제 움직임에 훨씬 직접적으로 연동되도록 개선했습니다. 다만 운임선물 특성상 변동성이 매우 크고, 2018년 이전 이력은 없습니다.</t>
+  </si>
+  <si>
+    <t>글로벌 벌크화물(철광석·석탄·곡물 등) 물동량 확대, 교역 활발 신호</t>
+  </si>
+  <si>
+    <t>글로벌 벌크화물 물동량 위축, 교역 둔화 신호</t>
+  </si>
+  <si>
+    <t>밸류에이션 배수</t>
+  </si>
+  <si>
+    <t>S&amp;P500 PER(일반)</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>multpl.com(Shiller 데이터 재정리)</t>
+  </si>
+  <si>
+    <t>https://www.multpl.com/</t>
+  </si>
+  <si>
+    <t>현재 주가를 최근 1년 실적(EPS)으로 나눈 값 - 가장 널리 쓰이는 밸류에이션 지표</t>
+  </si>
+  <si>
+    <t>CAPE보다 단기 실적 변동에 민감해서, 경기침체 직후 이익이 급감하면 오히려 PER이 비정상적으로 치솟는 왜곡이 나타날 수 있습니다.</t>
+  </si>
+  <si>
+    <t>고평가 신호(단, 이익 급감기에는 왜곡 가능성 있음)</t>
+  </si>
+  <si>
+    <t>저평가 신호</t>
+  </si>
+  <si>
+    <t>S&amp;P500 CAPE(실러PER)</t>
+  </si>
+  <si>
+    <t>cape</t>
+  </si>
+  <si>
+    <t>최근 10년치 물가조정 평균 실적으로 나눈 PER - 노벨경제학상 수상자 로버트 실러가 고안</t>
+  </si>
+  <si>
+    <t>10년 평균을 사용해 경기순환에 따른 일시적 실적 왜곡을 완화한 지표입니다. 역사적으로 CAPE가 높을수록 이후 10년간의 실질수익률이 낮게 나타나는 경향이 반복적으로 확인됐습니다. S&amp;P500 주가를 그대로 포함하는 지표라 S&amp;P500과의 상관계수 자체는 구조적으로 항상 높게 나오므로, 상관관계보다 '절대 수준'을 보는 것이 중요합니다.</t>
+  </si>
+  <si>
+    <t>고평가 신호(장기적으로 낮은 기대수익률과 연관되는 경향이 반복 확인됨)</t>
+  </si>
+  <si>
+    <t>저평가 신호(장기적으로 높은 기대수익률과 연관되는 경향이 반복 확인됨)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 PBR(주가순자산)</t>
+  </si>
+  <si>
+    <t>price_to_book</t>
+  </si>
+  <si>
+    <t>주가를 기업의 순자산(장부가치)으로 나눈 값</t>
+  </si>
+  <si>
+    <t>자산 중심 산업(금융, 제조업)의 밸류에이션 평가에는 유용하나, 무형자산 비중이 큰 기술기업에는 왜곡이 있을 수 있습니다.</t>
+  </si>
+  <si>
+    <t>고평가 신호(단, 무형자산 비중이 큰 업종에는 왜곡 가능성)</t>
+  </si>
+  <si>
+    <t>저평가 신호(단, 무형자산 비중이 큰 업종에는 왜곡 가능성)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 ROE(자기자본이익률, %)</t>
+  </si>
+  <si>
+    <t>roe</t>
+  </si>
+  <si>
+    <t>multpl(PBR÷PER), 자체 계산(정확한 항등식)</t>
+  </si>
+  <si>
+    <t>기업이 주주 자본(순자산) 대비 얼마나 효율적으로 이익을 내는지 보여주는 대표적 수익성 지표</t>
+  </si>
+  <si>
+    <t>ROE = 이익 ÷ 순자산. PBR(주가÷순자산)과 PER(주가÷이익)의 비율(PBR÷PER = 이익÷순자산)로 계산합니다. 같은 시점의 '주가'가 분자·분모에서 정확히 상쇄되므로 근사치가 아니라 수학적으로 정확한 값입니다.</t>
+  </si>
+  <si>
+    <t>자기자본 대비 수익성 개선</t>
+  </si>
+  <si>
+    <t>자기자본 대비 수익성 악화, 또는 자사주매입·배당으로 순자산이 줄어든 영향일 수도 있음</t>
+  </si>
+  <si>
+    <t>S&amp;P500 배당수익률(%)</t>
+  </si>
+  <si>
+    <t>dividend_yield</t>
+  </si>
+  <si>
+    <t>주가 대비 연간 배당금의 비율</t>
+  </si>
+  <si>
+    <t>채권금리와 비교해 주식의 상대적 매력을 가늠하는 전통적 지표입니다.</t>
+  </si>
+  <si>
+    <t>배당수익률 하락(주가 상승에 따른): 밸류에이션 부담 신호로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>배당수익률 상승(주가 하락에 따른): 상대적으로 매력적인 진입 구간으로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>S&amp;P500 이익수익률(%)</t>
+  </si>
+  <si>
+    <t>earnings_yield</t>
+  </si>
+  <si>
+    <t>PER의 역수(EPS/주가) - 주식을 채권처럼 봤을 때의 '수익률'</t>
+  </si>
+  <si>
+    <t>국채금리와 비교해 주식이 채권 대비 상대적으로 매력적인지 판단하는 데 쓰이는 지표입니다('Fed 모델'이라는 접근의 핵심 개념).</t>
+  </si>
+  <si>
+    <t>이익수익률이 국채금리보다 크게 낮으면: 채권 대비 주식 매력 저하 신호로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>이익수익률이 국채금리보다 크게 높으면: 채권 대비 주식 매력 상승 신호로 해석되는 경우가 많음</t>
+  </si>
+  <si>
+    <t>S&amp;P500 PEG비율(트레일링 근사)</t>
+  </si>
+  <si>
+    <t>peg</t>
+  </si>
+  <si>
+    <t>multpl(PER)+Yahoo Finance(가격) 조합, 자체 계산</t>
+  </si>
+  <si>
+    <t>https://www.multpl.com/s-p-500-pe-ratio</t>
+  </si>
+  <si>
+    <t>PER을 이익성장률로 나눠, '성장성 대비 얼마나 비싼가'를 보는 지표 (1.0 근처가 적정으로 통용됨)</t>
+  </si>
+  <si>
+    <t>PEG = PER ÷ 이익성장률(%). 전설적 투자자 피터 린치가 대중화한 지표로, 단순 PER만으로는 '성장이 빠른 기업(정당화되는 고PER)'과 '성장 없이 비싸기만 한 기업'을 구분 못 한다는 한계를 보완합니다. 정통 PEG는 애널리스트의 '향후' 이익성장률 전망치를 쓰지만, 이 전망치는 무료로 자동 수집할 수 있는 공개 소스가 없습니다(Yardeni·GuruFocus 등 유료). 이 대시보드의 PEG는 대신 실제 EPS의 '과거(trailing)' 12개월 성장률로 근사한 대체 지표이며, 미래 기대가 아닌 과거 실적 기준이라 전망치 기반 PEG보다 후행적입니다. 이익이 역성장(마이너스)한 구간은 PEG 정의상 의미가 없어 데이터에서 제외됩니다.</t>
+  </si>
+  <si>
+    <t>이익성장 대비 주가가 비싸지는 국면(단, 성장률 자체가 낮아져서 PEG가 오른 것인지 주가만 오른 것인지 구분 필요)</t>
+  </si>
+  <si>
+    <t>이익성장 대비 주가가 저렴해지는 국면(성장률이 빨라져서 낮아진 것이라면 오히려 긍정적 신호)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 PSR(주가매출)</t>
+  </si>
+  <si>
+    <t>price_to_sales</t>
+  </si>
+  <si>
+    <t>주가를 기업의 매출로 나눈 값</t>
+  </si>
+  <si>
+    <t>아직 이익을 내지 못하는 성장기업(적자 스타트업 등) 밸류에이션을 평가할 때 특히 유용하게 쓰이는 지표입니다.</t>
+  </si>
+  <si>
+    <t>고평가 신호</t>
+  </si>
+  <si>
+    <t>S&amp;P500 배당성향(Payout Ratio, %)</t>
+  </si>
+  <si>
+    <t>payout</t>
+  </si>
+  <si>
+    <t>multpl(배당수익률×PER), 자체 계산(정확한 항등식)</t>
+  </si>
+  <si>
+    <t>기업이 번 이익 중 몇 %를 배당으로 나눠주는지 보여주는 지표</t>
+  </si>
+  <si>
+    <t>배당성향 = 배당 ÷ 이익. 배당수익률과 PER을 곱하면 주가가 상쇄되어 배당/이익이 정확히 산출됩니다. 최근 수십 년간 미국 기업들이 배당보다 자사주매입을 선호하는 추세로 바뀌면서 이 비율 자체가 구조적으로 낮아져 왔다는 점을 감안해서 봐야 합니다.</t>
+  </si>
+  <si>
+    <t>이익 중 더 많은 몫을 배당으로 지급</t>
+  </si>
+  <si>
+    <t>이익 대비 배당 지급 비중 축소(재투자 확대 또는 자사주매입 선호)</t>
+  </si>
+  <si>
+    <t>미국 기업이익률(GDP대비, %)</t>
+  </si>
+  <si>
+    <t>CP/GDP</t>
+  </si>
+  <si>
+    <t>FRED(CP÷GDP), 자체 계산</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/CP</t>
+  </si>
+  <si>
+    <t>미국 전체 기업이 벌어들인 이익이 국가경제(GDP) 전체에서 차지하는 비중</t>
+  </si>
+  <si>
+    <t>FRED 공식 기업이익(CP) ÷ 명목GDP로 계산됩니다. '지금 기업 마진이 역사적으로 높은 수준인지'를 가늠할 수 있는 대표적인 무료 매크로 프록시입니다.</t>
+  </si>
+  <si>
+    <t>기업 부문이 경제 전체에서 더 많은 몫을 가져가는 국면</t>
+  </si>
+  <si>
+    <t>기업이익 비중 축소</t>
+  </si>
+  <si>
+    <t>복합·추세지표</t>
+  </si>
+  <si>
+    <t>버핏지수(시총/GDP, %)</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>FRED(시가총액) + FRED(GDP), 자체 계산</t>
+  </si>
+  <si>
+    <t>미국 전체 상장주식 시가총액을 GDP로 나눈 값 - 워런 버핏이 '최고의 단일 밸류에이션 지표'라 언급했던 지표</t>
+  </si>
+  <si>
+    <t>100%를 넘으면 주식시장 규모가 실물경제보다 커졌다는 뜻으로, 역사적으로 높을수록 이후 장기수익률이 낮게 나타나는 경향이 있습니다. 다만 저금리 시대, 미국 기업의 해외매출 비중 증가 등 구조적 요인으로 '정상' 기준선 자체가 과거보다 높아졌다는 지적도 있어, 절대 기준보다는 참고 지표로 활용하는 것이 안전합니다.</t>
+  </si>
+  <si>
+    <t>고평가 신호(장기적으로 낮은 기대수익률과 연관되는 경향)</t>
+  </si>
+  <si>
+    <t>저평가 신호(장기적으로 높은 기대수익률과 연관되는 경향)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 추세이격률(%)</t>
+  </si>
+  <si>
+    <t>S&amp;P500이 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
+  </si>
+  <si>
+    <t>지수의 절대 레벨이 아니라, '역사적 추세 대비 지금이 과열·침체 국면인지'를 판단하는 용도로 쓰입니다.</t>
+  </si>
+  <si>
+    <t>버핏지수 추세이격률(%)</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>버핏지수 기반 자체 계산(추세선 대비 이격도)</t>
+  </si>
+  <si>
+    <t>버핏지수가 자기 자신의 장기 추세선 대비 몇 % 위/아래에 있는지</t>
+  </si>
+  <si>
+    <t>절대수준(100%, 200% 등)보다 '추세 대비 이례적인 수준인지'를 보는 보조지표입니다.</t>
+  </si>
+  <si>
+    <t>양수: 추세선 위(고평가 국면)</t>
+  </si>
+  <si>
+    <t>음수: 추세선 아래(저평가 국면)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 CAPE 추세이격률(%)</t>
+  </si>
+  <si>
+    <t>CAPE(실러PER) 자체가 CAPE의 장기 추세선 대비 몇 % 위/아래에 있는지</t>
+  </si>
+  <si>
+    <t>밸류에이션 지표(CAPE)의 '밸류에이션'을 다시 보는 2차 지표로, CAPE 절대수준만으로는 놓치기 쉬운 '추세 이탈 정도'를 보완합니다.</t>
+  </si>
+  <si>
+    <t>양수: CAPE 추세선 위(밸류에이션이 자기 역사보다도 더 이례적으로 높음)</t>
+  </si>
+  <si>
+    <t>음수: CAPE 추세선 아래</t>
+  </si>
+  <si>
+    <t>나스닥100 추세이격률(%)</t>
+  </si>
+  <si>
+    <t>나스닥100이 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
+  </si>
+  <si>
+    <t>S&amp;P500 추세이격률과 같은 개념을 나스닥100에 적용한 지표로, 기술주 특유의 과열/침체 국면 판단에 활용됩니다.</t>
+  </si>
+  <si>
+    <t>S&amp;P500 월간수익률(%)</t>
+  </si>
+  <si>
+    <t>S&amp;P500의 전월 대비 등락률</t>
+  </si>
+  <si>
+    <t>절대 가격(추세형) 지표가 아닌 '변화율(정체형)' 지표라, GDP성장률처럼 이미 변화율인 지표와 짝지어 비교할 때 허위상관(추세 혼입)을 피할 수 있어 유용합니다.</t>
+  </si>
+  <si>
+    <t>나스닥100 월간수익률(%)</t>
+  </si>
+  <si>
+    <t>나스닥100의 전월 대비 등락률</t>
+  </si>
+  <si>
+    <t>S&amp;P500 월간수익률과 같은 용도로, 기술주 지수의 변화율만 따로 비교하고 싶을 때 사용합니다.</t>
+  </si>
+  <si>
+    <t>지표 개수</t>
+  </si>
+  <si>
+    <t>합계</t>
+  </si>
+  <si>
+    <t>변경사항</t>
+  </si>
+  <si>
+    <t>① 신규 카테고리 '한국 주요지표' 추가 (15개 지표) — 기존 8개 카테고리 → 9개로 확장</t>
+  </si>
+  <si>
+    <t>② 한국 CPI, 한국 명목GDP, 한국 기준금리, 한국 M2 통화량, 한국 무역수지, 한국 경상수지 신규 추가</t>
+  </si>
+  <si>
+    <t>③ 코스피 → 코스피지수, 코스닥 → 코스닥지수로 이름 변경 및 '지수·주가'에서 '한국 주요지표'로 이동</t>
+  </si>
+  <si>
+    <t>④ 코스피 시가총액, KOSPI PER, KOSPI PBR, KOSPI 배당수익률 신규 추가 (KOSIS 연동)</t>
+  </si>
+  <si>
+    <t>⑤ 코스피 추세이격률(%), 코스피 월간수익률(%)을 '복합·추세지표'에서 '한국 주요지표'로 이동</t>
+  </si>
+  <si>
+    <t>⑥ 한국 기준금리·M2는 ECOS(한국은행), KOSPI PER/PBR/배당수익률/시가총액은 KOSIS(국가통계포털) API 신규 연동</t>
+  </si>
+  <si>
+    <t>⑦ '밸류에이션(복합지표)' 카테고리를 '밸류에이션 배수'와 '복합·추세지표'로 분리</t>
+  </si>
+  <si>
+    <t>⑧ S&amp;P500 ROE, 배당성향(Payout Ratio), 미국 기업이익률(GDP대비) 신규 추가</t>
+  </si>
+  <si>
+    <t>⑨ 미국 거시지표: 명목GDP를 CPI 이전으로, 비농업고용자수를 실업률 다음으로 순서 변경</t>
+  </si>
+  <si>
+    <t>⑩ 지수·주가: 코스피/코스닥 제거 후 지수→시가총액→VIX→CBOE 순으로 재배열</t>
+  </si>
+  <si>
+    <t>⑪ 각 카테고리 내부는 주가 관련성·시장 주목도가 높은 지표 순으로 재배열</t>
+  </si>
+  <si>
+    <t>코스피지수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>코스닥지수</t>
-  </si>
-  <si>
-    <t>^KQ11</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/^KQ11</t>
-  </si>
-  <si>
-    <t>중소·벤처·기술주 중심의 코스닥 시장 종합주가지수 — 미국의 나스닥에 대응하는 성격</t>
-  </si>
-  <si>
-    <t>코스피보다 변동성이 크고, 바이오·2차전지·IT 등 성장주 비중이 높아 위험선호(리스크온) 심리에 민감하게 반응하는 경향이 있습니다.</t>
-  </si>
-  <si>
-    <t>성장주·중소형주 중심 위험선호 심리 확대</t>
-  </si>
-  <si>
-    <t>성장주·중소형주 중심 위험회피 심리 확대</t>
-  </si>
-  <si>
-    <t>코스피 시가총액</t>
-  </si>
-  <si>
-    <t>market_cap</t>
-  </si>
-  <si>
-    <t>KOSIS(국가통계포털)</t>
-  </si>
-  <si>
-    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0029</t>
-  </si>
-  <si>
-    <t>코스피(코스닥 제외) 상장기업 전체의 시가총액 합계</t>
-  </si>
-  <si>
-    <t>KOSIS(국가통계포털) 공식 데이터. S&amp;P500이 미국 대형주 중심 지수이듯, 코스피도 한국 대형주 중심 시장이라 이 둘을 나란히 비교하는 것이 가장 적절한 대응관계입니다.</t>
-  </si>
-  <si>
-    <t>한국 대형주 시장 전체 가치 확대</t>
-  </si>
-  <si>
-    <t>한국 대형주 시장 전체 가치 축소</t>
-  </si>
-  <si>
-    <t>KOSPI PER(일반)</t>
-  </si>
-  <si>
-    <t>per</t>
-  </si>
-  <si>
-    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0033</t>
-  </si>
-  <si>
-    <t>코스피 상장기업 전체의 평균 주가수익비율 — 이익 대비 코스피가 얼마나 비싼지</t>
-  </si>
-  <si>
-    <t>KOSIS(국가통계포털) 공식 데이터. S&amp;P500 PER과 같은 개념으로, 한미 증시의 상대적 밸류에이션을 직접 비교할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>이익 대비 코스피가 비싸지는 국면</t>
-  </si>
-  <si>
-    <t>이익 대비 코스피가 저렴해지는 국면</t>
-  </si>
-  <si>
-    <t>KOSPI PBR</t>
-  </si>
-  <si>
-    <t>pbr</t>
-  </si>
-  <si>
-    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0034</t>
-  </si>
-  <si>
-    <t>코스피 상장기업 전체의 평균 주가순자산비율 — 장부가치 대비 코스피가 얼마나 비싼지</t>
-  </si>
-  <si>
-    <t>KOSIS(국가통계포털) 공식 데이터. 한국 증시는 전통적으로 미국 대비 PBR이 낮게(디스카운트) 형성되는 경향이 있어('코리아 디스카운트' 논의), 이 지표로 그 정도를 추적할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>장부가치 대비 코스피가 비싸지는 국면(디스카운트 축소)</t>
-  </si>
-  <si>
-    <t>장부가치 대비 코스피가 저렴해지는 국면(디스카운트 확대)</t>
-  </si>
-  <si>
-    <t>KOSPI 배당수익률(%)</t>
-  </si>
-  <si>
-    <t>dividend</t>
-  </si>
-  <si>
-    <t>https://kosis.kr/statHtml/statHtml.do?orgId=343&amp;tblId=DT_343_2010_S0032</t>
-  </si>
-  <si>
-    <t>코스피 상장기업 전체의 평균 배당수익률</t>
-  </si>
-  <si>
-    <t>KOSIS(국가통계포털) 공식 데이터. 배당수익률이 국채금리보다 높은지 낮은지는 주식 대비 채권의 상대적 매력을 가늠하는 전통적 잣대 중 하나입니다.</t>
-  </si>
-  <si>
-    <t>배당 매력 확대(주가 하락 또는 배당 확대)</t>
-  </si>
-  <si>
-    <t>배당 매력 축소(주가 상승 또는 배당 축소)</t>
-  </si>
-  <si>
-    <t>코스피 추세이격률(%)</t>
-  </si>
-  <si>
-    <t>해당 원본 지표 기반 자체 계산(추세선 대비 이격도)</t>
-  </si>
-  <si>
-    <t>코스피가 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
-  </si>
-  <si>
-    <t>S&amp;P500 추세이격률과 같은 개념을 코스피에 적용한 지표입니다.</t>
-  </si>
-  <si>
-    <t>양수: 추세선 위(과열 국면 가능성)</t>
-  </si>
-  <si>
-    <t>음수: 추세선 아래(침체 국면 가능성)</t>
-  </si>
-  <si>
-    <t>코스피 월간수익률(%)</t>
-  </si>
-  <si>
-    <t>해당 원본 지표 기반 자체 계산(전월대비 수익률)</t>
-  </si>
-  <si>
-    <t>코스피의 전월 대비 등락률</t>
-  </si>
-  <si>
-    <t>S&amp;P500 월간수익률과 같은 용도로, 한국 증시의 변화율만 따로 비교하고 싶을 때 사용합니다.</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>미국 거시지표</t>
-  </si>
-  <si>
-    <t>미국 명목GDP</t>
-  </si>
-  <si>
-    <t>GDP</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/GDP</t>
-  </si>
-  <si>
-    <t>물가상승분을 빼지 않은, 달러로 표시한 미국 경제 전체의 크기</t>
-  </si>
-  <si>
-    <t>실질GDP와 달리 인플레이션 효과가 그대로 포함돼 있어, 실질GDP와 함께 봐야 '진짜 성장'과 '물가상승에 의한 착시'를 구분할 수 있습니다. 버핏지수(시총/GDP)를 계산할 때 분모로도 쓰입니다.</t>
-  </si>
-  <si>
-    <t>경제 규모 확대(다만 물가상승만으로도 오를 수 있어 실질GDP와 함께 확인 필요)</t>
-  </si>
-  <si>
-    <t>디플레이션이나 심각한 경기침체 시에만 드물게 발생</t>
-  </si>
-  <si>
-    <t>미국 CPI</t>
-  </si>
-  <si>
-    <t>CPIAUCSL</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CPIAUCSL</t>
-  </si>
-  <si>
-    <t>소비자가 실제로 구매하는 상품·서비스 가격의 평균적인 변화율(물가상승률)</t>
-  </si>
-  <si>
-    <t>가장 대표적인 인플레이션 측정 지표로, 연준의 금리 결정에 핵심 참고자료로 쓰입니다. 통상 전월비·전년동월비로 인용됩니다.</t>
-  </si>
-  <si>
-    <t>인플레이션 압력 확대, 연준 긴축(금리인상) 가능성 상승 → 통상 주가에 부담</t>
-  </si>
-  <si>
-    <t>인플레이션 완화, 금리인하 기대 상승 → 통상 주가에 우호적</t>
-  </si>
-  <si>
-    <t>미국 실업률</t>
-  </si>
-  <si>
-    <t>UNRATE</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/UNRATE</t>
-  </si>
-  <si>
-    <t>일할 의사가 있는 사람 중 일자리를 구하지 못한 사람의 비율</t>
-  </si>
-  <si>
-    <t>가장 널리 알려진 노동시장 지표지만, 경기가 나빠진 뒤 뒤늦게 반응하는 대표적인 '후행지표'입니다.</t>
-  </si>
-  <si>
-    <t>경기 둔화 신호. 통상 주가에 부정적이나, 연준 금리인하 기대를 자극해 국면에 따라 우호적으로 작용하기도 함</t>
-  </si>
-  <si>
-    <t>고용시장 호조, 경기 개선 신호</t>
-  </si>
-  <si>
-    <t>비농업고용자수</t>
-  </si>
-  <si>
-    <t>PAYEMS</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/PAYEMS</t>
-  </si>
-  <si>
-    <t>농업을 제외한 미국 전체 취업자 수(전월 대비 변화분이 핵심)</t>
-  </si>
-  <si>
-    <t>매월 첫째 주 금요일에 발표되는 '고용보고서'의 핵심 지표로, 시장이 가장 민감하게 반응하는 경제지표 중 하나입니다. 예상치와 크게 어긋나면 주가·금리 변동성이 커집니다.</t>
-  </si>
-  <si>
-    <t>경기 호조 신호. 다만 예상보다 지나치게 강하면 연준 긴축 우려로 이어져 주가에 오히려 부담이 될 수 있음</t>
-  </si>
-  <si>
-    <t>경기 둔화 신호. 통상 주가에 부정적이나, 금리인하 기대를 자극하는 국면에서는 오히려 주가에 우호적으로 해석되기도 함</t>
-  </si>
-  <si>
-    <t>ISM 제조업 PMI</t>
-  </si>
-  <si>
-    <t>ISM/pmi/pm</t>
-  </si>
-  <si>
-    <t>DBnomics(ISM 원자료 재배포, 무료 대안소스)</t>
-  </si>
-  <si>
-    <t>https://db.nomics.world/ISM/pmi/pm</t>
-  </si>
-  <si>
-    <t>제조업 구매관리자들을 설문해 만든 경기 체감 지수(50 기준)</t>
-  </si>
-  <si>
-    <t>50 이상이면 확장, 이하이면 위축 국면을 의미하는 대표적 심리 서베이 지표입니다. FRED의 기존 코드(NAPM)는 2016년 이후 갱신이 중단돼, 무료 대안인 DBnomics 재배포 데이터를 사용합니다. 공식 소스가 아니므로 연동 전 데이터 정합성 검증이 필요합니다.</t>
-  </si>
-  <si>
-    <t>제조업 경기 확장 국면</t>
-  </si>
-  <si>
-    <t>제조업 경기 위축 국면</t>
-  </si>
-  <si>
-    <t>신규 실업급여 신청 건수</t>
-  </si>
-  <si>
-    <t>ICSA</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/ICSA</t>
-  </si>
-  <si>
-    <t>주간</t>
-  </si>
-  <si>
-    <t>한 주 동안 새로 실업급여를 신청한 사람 수</t>
-  </si>
-  <si>
-    <t>매주 목요일 발표되는 고속 노동시장 지표로, 월간 고용지표보다 훨씬 빠르게 경기 변화를 포착합니다. 변동성이 크므로 4주 이동평균과 함께 보는 것이 일반적입니다.</t>
-  </si>
-  <si>
-    <t>고용시장 냉각 신호, 경기둔화 우려 확대</t>
-  </si>
-  <si>
-    <t>고용시장 견조, 경기 호조 신호</t>
-  </si>
-  <si>
-    <t>미국 실질GDP성장률</t>
-  </si>
-  <si>
-    <t>A191RL1Q225SBEA</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/A191RL1Q225SBEA</t>
-  </si>
-  <si>
-    <t>물가상승 효과를 뺀, 미국 경제 전체가 얼마나 빠르게 성장했는지를 보여주는 지표(연율 환산)</t>
-  </si>
-  <si>
-    <t>미국에서 일정 기간 생산된 모든 재화·서비스의 가치를 물가변동 효과를 제거하고 측정한, 경제 전체의 '건강 상태'를 보여주는 가장 포괄적인 지표입니다. 속보치→잠정치→확정치 순으로 한 분기에 세 차례 수정 발표됩니다.</t>
-  </si>
-  <si>
-    <t>경기 확장 국면, 기업이익 개선 기대. 다만 지나치게 높으면 과열·인플레이션 우려로 연준 긴축을 유발할 수 있음</t>
-  </si>
-  <si>
-    <t>경기 둔화·침체 신호. 2분기 연속 마이너스면 통상 '기술적 침체'로 불리나, 미국의 공식 경기침체 판정은 NBER이 별도 기준으로 결정함</t>
-  </si>
-  <si>
-    <t>근원 CPI</t>
-  </si>
-  <si>
-    <t>CPILFESL</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CPILFESL</t>
-  </si>
-  <si>
-    <t>변동성이 큰 식품·에너지 가격을 뺀, 물가의 '기조적인' 흐름</t>
-  </si>
-  <si>
-    <t>일시적인 유가 급등락 같은 노이즈를 제거해 물가의 진짜 추세를 보기 위한 지표입니다. 연준이 일반 CPI보다 더 중요하게 참고하는 경우가 많습니다.</t>
-  </si>
-  <si>
-    <t>CPI와 동일하게 해석하되, 연준의 정책 판단에 더 직접적인 영향을 미침</t>
-  </si>
-  <si>
-    <t>소매 매출액</t>
-  </si>
-  <si>
-    <t>RSAFS</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/RSAFS</t>
-  </si>
-  <si>
-    <t>미국 소비자가 한 달 동안 소매점에서 지출한 총액</t>
-  </si>
-  <si>
-    <t>미국 GDP의 약 2/3를 차지하는 개인소비 중 상품소비 부분을 가장 먼저 보여주는 지표로, 소비 심리와 실제 지출력을 함께 반영합니다.</t>
-  </si>
-  <si>
-    <t>소비 활력 확대, 경기 호조 신호(단 인플레이션에 의한 명목증가 여부 확인 필요)</t>
-  </si>
-  <si>
-    <t>소비 위축, 경기둔화 우려</t>
-  </si>
-  <si>
-    <t>개인소비지출(PCE)</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/PCE</t>
-  </si>
-  <si>
-    <t>미국 가계가 실제로 소비에 지출한 총액(연준이 가장 선호하는 물가지표의 기반)</t>
-  </si>
-  <si>
-    <t>GDP의 소비 항목을 구성하며, 여기서 산출되는 PCE 물가지수는 연준이 CPI보다 더 중시하는 인플레이션 지표입니다.</t>
-  </si>
-  <si>
-    <t>소비 확대, 경기 호조(과열 시 인플레이션 우려)</t>
-  </si>
-  <si>
-    <t>소비 위축, 경기둔화 신호</t>
-  </si>
-  <si>
-    <t>미국 PPI</t>
-  </si>
-  <si>
-    <t>PPIACO</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/PPIACO</t>
-  </si>
-  <si>
-    <t>기업(생산자)이 판매하는 단계에서의 가격 변화 - 소비자물가(CPI)의 '선행지표' 성격</t>
-  </si>
-  <si>
-    <t>원자재-중간재-완제품 단계에서 발생하는 가격 압력을 포착합니다. PPI가 오르면 몇 달 뒤 CPI에도 반영되는 경우가 많아 인플레이션의 조기경보 역할을 합니다.</t>
-  </si>
-  <si>
-    <t>기업 원가 부담 증가 → 마진 압박, 또는 가격전가로 인한 소비자물가 상승 우려</t>
-  </si>
-  <si>
-    <t>원가 부담 완화, 인플레이션 압력 둔화 신호</t>
-  </si>
-  <si>
-    <t>미국 산업생산지수</t>
-  </si>
-  <si>
-    <t>INDPRO</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/INDPRO</t>
-  </si>
-  <si>
-    <t>공장·광산·유틸리티 등 실물 생산활동의 크기를 지수로 나타낸 지표</t>
-  </si>
-  <si>
-    <t>서비스업 비중이 커진 현대 경제에서 예전만큼 비중은 크지 않지만, 여전히 제조업 경기 사이클을 판단하는 핵심 지표로 쓰입니다.</t>
-  </si>
-  <si>
-    <t>제조업 경기 확장, 경기 호조 신호</t>
-  </si>
-  <si>
-    <t>제조업 위축, 경기 둔화 신호. 여러 달 연속 하락하면 경기침체 전조로 해석되기도 함</t>
-  </si>
-  <si>
-    <t>미국 소비자심리지수</t>
-  </si>
-  <si>
-    <t>UMCSENT</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/UMCSENT</t>
-  </si>
-  <si>
-    <t>미시간대 설문조사로 집계하는, 소비자들이 경제를 얼마나 낙관/비관하는지 나타내는 지수</t>
-  </si>
-  <si>
-    <t>실제 소비지출로 이어지기 전 소비자들의 '기대심리'를 미리 포착하는 선행지표 성격을 갖습니다. 미국 GDP의 약 70%가 소비지출이라 중요도가 높습니다.</t>
-  </si>
-  <si>
-    <t>소비 확대 기대, 경기에 우호적</t>
-  </si>
-  <si>
-    <t>소비 위축 우려, 경기 둔화 신호</t>
-  </si>
-  <si>
-    <t>OECD 경기선행지수(미국, CLI)</t>
-  </si>
-  <si>
-    <t>USALOLITONOSTSAM</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/USALOLITONOSTSAM</t>
-  </si>
-  <si>
-    <t>OECD가 여러 선행 지표를 종합해 만든 경기 국면 판단 지수(100 기준)</t>
-  </si>
-  <si>
-    <t>OECD가 직접 산출하며, FRED가 그대로 미러링해 제공하기 때문에 기존 FRED 파이프라인으로 바로 수집 가능합니다. 100을 기준으로 상회/하회 여부와 추세 방향이 핵심입니다.</t>
-  </si>
-  <si>
-    <t>경기 확장 국면 진입 신호</t>
-  </si>
-  <si>
-    <t>경기 둔화·침체 국면 진입 신호</t>
-  </si>
-  <si>
-    <t>개인소득</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/PI</t>
-  </si>
-  <si>
-    <t>미국 가계가 임금, 이자, 배당, 이전소득 등으로 벌어들인 총소득</t>
-  </si>
-  <si>
-    <t>개인소비지출(PCE)과 함께 발표되는 '개인소득 및 지출' 보고서의 핵심 항목으로, 소비 여력의 원천을 보여줍니다.</t>
-  </si>
-  <si>
-    <t>소비 여력 확대 기대</t>
-  </si>
-  <si>
-    <t>소비 위축 가능성</t>
-  </si>
-  <si>
-    <t>내구재 수주</t>
-  </si>
-  <si>
-    <t>DGORDER</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGORDER</t>
-  </si>
-  <si>
-    <t>3년 이상 사용 가능한 내구재(자동차, 기계 등)에 대한 신규 주문 총액</t>
-  </si>
-  <si>
-    <t>기업의 설비투자 의지를 보여주는 선행지표로, 변동성이 큰 항공기 주문을 제외한 '핵심자본재수주'도 함께 참고하는 것이 일반적입니다.</t>
-  </si>
-  <si>
-    <t>기업 투자심리 개선, 향후 생산 확대 기대</t>
-  </si>
-  <si>
-    <t>기업 투자심리 위축, 향후 생산 둔화 우려</t>
-  </si>
-  <si>
-    <t>신규 주택허가 건수</t>
-  </si>
-  <si>
-    <t>PERMIT</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/PERMIT</t>
-  </si>
-  <si>
-    <t>한 달 동안 새로 발급된 신규 주택 건축 허가 건수</t>
-  </si>
-  <si>
-    <t>실제 착공(HOUST)보다 한 단계 앞서 발생하는 절차라 주택시장의 '선행지표' 성격이 더 강합니다.</t>
-  </si>
-  <si>
-    <t>주택시장 활황 기대, 향후 착공 증가 신호</t>
-  </si>
-  <si>
-    <t>주택시장 위축 신호</t>
-  </si>
-  <si>
-    <t>중장비트럭 판매량(선행지표)</t>
-  </si>
-  <si>
-    <t>HTRUCKSSAAR</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/HTRUCKSSAAR</t>
-  </si>
-  <si>
-    <t>물류·건설 등에 쓰이는 대형 트럭의 판매량 - 실물경기의 '선행지표'로 활용되는 지표</t>
-  </si>
-  <si>
-    <t>기업들이 향후 물동량 증가를 예상할 때 미리 트럭을 구매하는 경향이 있어, 공식 경기지표보다 몇 달 앞서 반응하는 경우가 많다고 알려져 있습니다.</t>
-  </si>
-  <si>
-    <t>향후 경기 확장 기대</t>
-  </si>
-  <si>
-    <t>향후 경기 둔화 우려</t>
-  </si>
-  <si>
-    <t>미국 경기침체확률(Chauvet-Piger)</t>
-  </si>
-  <si>
-    <t>RECPROUSM156N</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/RECPROUSM156N</t>
-  </si>
-  <si>
-    <t>여러 경제지표를 통계모델로 종합해 산출한, '지금이 경기침체 국면일 확률'(%)</t>
-  </si>
-  <si>
-    <t>세인트루이스 연준이 제공하는 모델 기반 지표로, 사람의 주관적 판단이 아니라 통계적으로 침체 여부를 추정합니다.</t>
-  </si>
-  <si>
-    <t>침체 가능성 확대(통상 50%를 넘으면 침체 국면 진입 가능성이 높다고 해석)</t>
-  </si>
-  <si>
-    <t>침체 가능성 낮음, 경기 안정적</t>
-  </si>
-  <si>
-    <t>금리·통화</t>
-  </si>
-  <si>
-    <t>미국 10년 국채금리</t>
-  </si>
-  <si>
-    <t>DGS10</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS10</t>
-  </si>
-  <si>
-    <t>만기 10년짜리 미국 국채에 적용되는 시장금리 - 주식 밸류에이션의 할인율, 모기지 금리의 기준으로 쓰이는 '만능 기준금리'</t>
-  </si>
-  <si>
-    <t>국채금리는 만기가 길수록 통상 더 높은 것이 정상입니다(장기 투자 리스크 프리미엄). 10년물은 전 세계 자산가격에 가장 폭넓은 영향을 미치는 금리입니다.</t>
-  </si>
-  <si>
-    <t>대출비용 상승, 채권가격 하락, 성장주 밸류에이션 부담</t>
-  </si>
-  <si>
-    <t>대출비용 하락, 채권가격 상승, 밸류에이션 부담 완화</t>
-  </si>
-  <si>
-    <t>미국 기준금리(FFR, 실효금리)</t>
-  </si>
-  <si>
-    <t>FEDFUNDS</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
-  </si>
-  <si>
-    <t>은행 간 초단기 자금 거래에 적용되는 금리 - 연준 통화정책의 핵심 수단</t>
-  </si>
-  <si>
-    <t>연준이 직접 통제하는 정책금리로, 대출·예금·채권 등 다른 모든 금리의 기준점 역할을 합니다. FOMC 회의에서 목표 범위를 정하고, 실효금리는 그 범위 안에서 실제 거래된 평균금리입니다.</t>
-  </si>
-  <si>
-    <t>긴축 국면, 대출비용 증가 → 통상 주가에 부담</t>
-  </si>
-  <si>
-    <t>완화 국면, 대출비용 감소 → 통상 주가에 우호적</t>
-  </si>
-  <si>
-    <t>미국 2Y-10Y 금리차</t>
-  </si>
-  <si>
-    <t>T10Y2Y</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/T10Y2Y</t>
-  </si>
-  <si>
-    <t>10년물 금리에서 2년물 금리를 뺀 값 - 장단기 금리차(수익률곡선의 기울기)</t>
-  </si>
-  <si>
-    <t>정상적인 경우 장기금리가 단기금리보다 높아 이 값은 양수입니다. 이 값이 음수로 뒤집히는 '역전' 현상은 역사적으로 경기침체를 앞서 예고해온 대표적 선행지표입니다.</t>
-  </si>
-  <si>
-    <t>정상 상태(플러스). 역전 이후 정상화되는 시점이 오히려 침체 시작과 겹치는 경우도 있어 해석에 주의가 필요함</t>
-  </si>
-  <si>
-    <t>역전(마이너스): 경기침체 경고 신호. 다만 실제 침체까지 통상 12~24개월의 시차가 있어 즉각적인 신호는 아님</t>
-  </si>
-  <si>
-    <t>달러인덱스(DXY)</t>
-  </si>
-  <si>
-    <t>DX-Y.NYB</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/DX-Y.NYB</t>
-  </si>
-  <si>
-    <t>유로, 엔, 파운드 등 주요 6개 통화 대비 달러의 종합적인 강세/약세를 나타내는 지수</t>
-  </si>
-  <si>
-    <t>특정 한 통화쌍이 아니라 '달러 전체의 힘'을 보여줍니다. 달러 강세는 신흥국 자금 이탈, 원자재 가격 하락, 미국 다국적기업의 해외실적 환산 감소로 이어지는 경우가 많습니다.</t>
-  </si>
-  <si>
-    <t>달러 강세: 신흥국·원자재·미국 다국적기업 해외실적에 부담</t>
-  </si>
-  <si>
-    <t>달러 약세: 신흥국·원자재·미국 다국적기업 해외실적에 우호적</t>
-  </si>
-  <si>
-    <t>미국 기준금리(목표, 계단식)</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>FRED(DFEDTAR+DFEDTARU 결합), 자체 계산</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DFEDTARU</t>
-  </si>
-  <si>
-    <t>연준이 FOMC에서 설정하는 기준금리 목표 범위(상단·하단을 상단값으로 계단식 통합)</t>
-  </si>
-  <si>
-    <t>연준은 2008년 12월 이전엔 단일 숫자로, 이후엔 범위(예: 5.25~5.50%)로 기준금리를 발표합니다. 이 지표는 2008년 이전 단일목표(DFEDTAR)와 이후 범위의 상단(DFEDTARU)을 하나로 이어붙여, 전체 역사를 계단식 그래프 하나로 볼 수 있게 만든 것입니다. 실효금리(FEDFUNDS)는 이 범위 안에서 실제 거래된 값이라 소폭 다르게 움직일 수 있습니다.</t>
-  </si>
-  <si>
-    <t>긴축(금리인상) 국면 — 대출비용 상승, 유동성 축소로 통상 주식·채권 등 위험자산에 부담</t>
-  </si>
-  <si>
-    <t>완화(금리인하) 국면 — 대출비용 하락, 유동성 확대로 통상 위험자산에 우호적</t>
-  </si>
-  <si>
-    <t>미국 M2 통화량</t>
-  </si>
-  <si>
-    <t>M2SL</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/M2SL</t>
-  </si>
-  <si>
-    <t>현금+예금+단기금융상품을 합친, 시중에 풀린 돈의 총량</t>
-  </si>
-  <si>
-    <t>통화량이 늘면 이론적으로 자산시장에 유입될 유동성이 늘어난다고 해석됩니다. 다만 실제 주가와의 관계는 시차가 있고 국면에 따라 불안정한 경우가 많습니다.</t>
-  </si>
-  <si>
-    <t>유동성 확대, 자산가격에 우호적일 수 있음</t>
-  </si>
-  <si>
-    <t>유동성 축소(드문 현상), 자산가격에 부담 요인</t>
-  </si>
-  <si>
-    <t>연준 자산규모(Fed B/S)</t>
-  </si>
-  <si>
-    <t>WALCL</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/WALCL</t>
-  </si>
-  <si>
-    <t>연준이 보유한 국채·MBS 등 자산의 총 규모 - 양적완화(QE)/양적긴축(QT) 여부를 보여주는 지표</t>
-  </si>
-  <si>
-    <t>연준이 채권을 사들이면(QE) 이 수치가 늘고 시중에 돈이 풀립니다. 반대로 팔거나 만기상환을 방치하면(QT) 줄어듭니다. 2020년 팬데믹 QE, 2022년 이후 QT가 대표적 사례입니다.</t>
-  </si>
-  <si>
-    <t>확대(QE): 유동성 공급, 통상 위험자산 가격에 우호적</t>
-  </si>
-  <si>
-    <t>축소(QT): 유동성 회수, 통상 위험자산 가격에 부담</t>
-  </si>
-  <si>
-    <t>미국 30년 모기지금리</t>
-  </si>
-  <si>
-    <t>MORTGAGE30US</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/MORTGAGE30US</t>
-  </si>
-  <si>
-    <t>미국 주택담보대출(30년 고정금리)의 평균 금리</t>
-  </si>
-  <si>
-    <t>미국 주택시장의 활황/침체를 가르는 핵심 변수입니다. 10년 국채금리에 연동되어 움직이는 경향이 있습니다.</t>
-  </si>
-  <si>
-    <t>주택구매 부담 증가, 주택경기 위축 우려</t>
-  </si>
-  <si>
-    <t>주택구매 부담 완화, 주택경기 개선 기대</t>
-  </si>
-  <si>
-    <t>미국 3개월 국채금리</t>
-  </si>
-  <si>
-    <t>DGS3MO</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS3MO</t>
-  </si>
-  <si>
-    <t>만기 3개월짜리 미국 국채에 적용되는 시장금리 - 연준 정책금리에 가장 민감하게 반응하는 단기금리</t>
-  </si>
-  <si>
-    <t>장단기 금리차를 계산할 때 10년물과 짝지어 자주 쓰이며, 연준 정책 변화를 가장 빠르게 반영하는 금리입니다.</t>
-  </si>
-  <si>
-    <t>단기 자금조달 비용 상승</t>
-  </si>
-  <si>
-    <t>단기 자금조달 비용 하락</t>
-  </si>
-  <si>
-    <t>미국 2년 국채금리</t>
-  </si>
-  <si>
-    <t>DGS2</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS2</t>
-  </si>
-  <si>
-    <t>만기 2년짜리 미국 국채에 적용되는 시장금리 - 향후 1~2년 연준 정책 경로에 대한 시장의 기대를 반영</t>
-  </si>
-  <si>
-    <t>10년물과의 금리차(2Y-10Y)가 경기침체 예측 지표로 널리 활용됩니다.</t>
-  </si>
-  <si>
-    <t>향후 긴축 기대 강화</t>
-  </si>
-  <si>
-    <t>향후 완화(금리인하) 기대 강화</t>
-  </si>
-  <si>
-    <t>엔/달러 환율</t>
-  </si>
-  <si>
-    <t>DEXJPUS</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DEXJPUS</t>
-  </si>
-  <si>
-    <t>1달러를 사는 데 필요한 엔화의 양</t>
-  </si>
-  <si>
-    <t>일본은행의 통화정책, 글로벌 '엔캐리 트레이드'(저금리 엔화를 빌려 다른 자산에 투자) 자금 흐름과 밀접하게 연동됩니다.</t>
-  </si>
-  <si>
-    <t>엔화 약세: 일본 수출기업에 유리, 엔캐리 트레이드 확대 유인</t>
-  </si>
-  <si>
-    <t>엔화 강세: 엔캐리 트레이드 청산 압력(글로벌 자산시장 변동성 확대 요인이 되기도 함)</t>
-  </si>
-  <si>
-    <t>지수·주가</t>
-  </si>
-  <si>
-    <t>S&amp;P500</t>
-  </si>
-  <si>
-    <t>^GSPC</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/^GSPC</t>
-  </si>
-  <si>
-    <t>미국 대형주 약 500개로 구성된, 미국 증시 전체를 대표하는 가장 널리 쓰이는 벤치마크 지수</t>
-  </si>
-  <si>
-    <t>시가총액 가중 방식으로 산출되어, 애플·마이크로소프트 등 초대형주의 영향력이 특히 큽니다.</t>
-  </si>
-  <si>
-    <t>나스닥100</t>
-  </si>
-  <si>
-    <t>^NDX</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/^NDX</t>
-  </si>
-  <si>
-    <t>나스닥 상장 비금융 대형주 100개로 구성된, 기술주 비중이 매우 높은 지수</t>
-  </si>
-  <si>
-    <t>성장주·기술주 성격이 강해 금리, 달러 변동에 S&amp;P500보다 더 민감하게 반응하는 경향이 있습니다.</t>
-  </si>
-  <si>
-    <t>다우존스</t>
-  </si>
-  <si>
-    <t>^DJI</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/^DJI</t>
-  </si>
-  <si>
-    <t>미국 우량 대형주 30개로 구성된, 가장 오래된 미국 주가지수</t>
-  </si>
-  <si>
-    <t>종목 수가 적고 가격가중 방식이라 S&amp;P500보다 대표성은 떨어지지만, 역사가 길어 여전히 널리 인용됩니다.</t>
-  </si>
-  <si>
-    <t>니케이225(일본)</t>
-  </si>
-  <si>
-    <t>^N225</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/^N225</t>
-  </si>
-  <si>
-    <t>일본 대표 기업 225개로 구성된 일본 증시 대표 지수</t>
-  </si>
-  <si>
-    <t>엔화 약세 국면에서 수출기업 실적 개선 기대로 상승하는 경향이 있어, 엔/달러 환율과 자주 함께 비교됩니다.</t>
-  </si>
-  <si>
-    <t>미국 전체 시가총액(조달러)</t>
-  </si>
-  <si>
-    <t>FRED(연준 Z.1 자금순환통계)</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BOGZ1LM893064105Q</t>
-  </si>
-  <si>
-    <t>미국 상장기업 전체의 시가총액 합계(연준 공식 집계, 조 달러 단위)</t>
-  </si>
-  <si>
-    <t>연준 Z.1 자금순환 통계(BOGZ1LM893064105Q)가 분기마다 집계하는, 미국 전체 상장기업 주식의 시가총액입니다. 버핏지수(시총/GDP)를 계산할 때 쓰는 분자와 동일한 원본 데이터이며, S&amp;P500 같은 개별 지수와 달리 신규상장·상장폐지·자사주매입 등 시장 전체의 물량 변화까지 반영합니다. 분기 발표라 일간 지수들과 달리 계단식으로 표시됩니다.</t>
-  </si>
-  <si>
-    <t>미국 주식시장 전체 가치 확대 — 경기 호조 또는 밸류에이션 확장을 반영</t>
-  </si>
-  <si>
-    <t>미국 주식시장 전체 가치 축소 — 경기 둔화 또는 밸류에이션 위축을 반영</t>
-  </si>
-  <si>
-    <t>VIX(변동성지수)</t>
-  </si>
-  <si>
-    <t>VIXCLS</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/VIXCLS</t>
-  </si>
-  <si>
-    <t>S&amp;P500 옵션 가격에서 역산한, 앞으로 30일간 예상되는 변동성 - 일명 '공포지수'</t>
-  </si>
-  <si>
-    <t>시장 참여자들이 얼마나 큰 가격 변동을 예상하는지를 보여주는 지표로, S&amp;P500 옵션의 내재변동성으로 산출되어 주가와 구조적으로 강한 음의 상관을 가집니다.</t>
-  </si>
-  <si>
-    <t>시장 불안·공포 확산, 통상 주가 하락과 동행</t>
-  </si>
-  <si>
-    <t>시장 안정·낙관, 통상 주가 상승과 동행</t>
-  </si>
-  <si>
-    <t>CBOE 풋/콜비율(주식)</t>
-  </si>
-  <si>
-    <t>equity</t>
-  </si>
-  <si>
-    <t>CBOE(공개 CSV, 2019.10 이후 갱신중단)</t>
-  </si>
-  <si>
-    <t>https://www.cboe.com/us/options/market_statistics/daily/</t>
-  </si>
-  <si>
-    <t>풋옵션(하락 베팅) 거래량을 콜옵션(상승 베팅) 거래량으로 나눈 비율</t>
-  </si>
-  <si>
-    <t>투자자들의 방향성 심리를 보여주는 지표입니다. 다만 단순 선형관계보다 '역발상(contrarian)' 지표로 활용됩니다.</t>
-  </si>
-  <si>
-    <t>비율이 극단적으로 낮음(다들 상승 베팅): 낙관 과잉, 고점 경계 신호로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>비율이 극단적으로 높음(다들 하락 베팅): 비관 과잉, 저점 근접 신호로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>신용·부채</t>
-  </si>
-  <si>
-    <t>하이일드 스프레드(HY OAS, CDS프록시)</t>
-  </si>
-  <si>
-    <t>BAMLH0A0HYM2</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLH0A0HYM2</t>
-  </si>
-  <si>
-    <t>신용등급이 낮은 회사채(정크본드) 금리가 안전한 국채금리보다 얼마나 더 높은지를 나타내는 '위험 프리미엄'</t>
-  </si>
-  <si>
-    <t>스프레드가 벌어질수록 투자자들이 신용위험을 더 크게 우려한다는 뜻입니다. 경기침체·금융위기 국면(2008, 2020, 2022년)에서 급등하는 경향을 보였습니다.</t>
-  </si>
-  <si>
-    <t>스프레드 확대: 신용경색, 위험회피 심리 확산, 통상 주가에 부담</t>
-  </si>
-  <si>
-    <t>스프레드 축소: 신용시장 안정, 위험선호 심리 확산, 통상 주가에 우호적</t>
-  </si>
-  <si>
-    <t>마진부채(FINRA, YoY%)</t>
-  </si>
-  <si>
-    <t>yoy</t>
-  </si>
-  <si>
-    <t>FINRA(공개 엑셀)</t>
-  </si>
-  <si>
-    <t>https://www.finra.org/investors/learn-to-invest/advanced-investing/margin-statistics</t>
-  </si>
-  <si>
-    <t>마진부채 잔액의 전년동월대비 증가율</t>
-  </si>
-  <si>
-    <t>절대 잔액보다 '변화 속도'를 보는 지표로, 나스닥100 등 성장주와 함께 움직이는 경향이 있다고 알려져 있습니다.</t>
-  </si>
-  <si>
-    <t>레버리지 증가 속도 가속, 투자심리 과열 가능성</t>
-  </si>
-  <si>
-    <t>레버리지 증가 속도 둔화 또는 감소, 위험회피 심리 확산</t>
-  </si>
-  <si>
-    <t>투자등급 스프레드(IG OAS)</t>
-  </si>
-  <si>
-    <t>BAMLC0A0CM</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLC0A0CM</t>
-  </si>
-  <si>
-    <t>우량 회사채(투자등급)와 국채 간 금리차 - 하이일드보다 안정적인 신용시장 온도계</t>
-  </si>
-  <si>
-    <t>하이일드 스프레드보다 변동성은 작지만 같은 방향으로 움직이며, 우량기업의 자금조달 여건을 보여줍니다.</t>
-  </si>
-  <si>
-    <t>스프레드 확대: 신용여건 악화(강도는 하이일드보다 약함)</t>
-  </si>
-  <si>
-    <t>스프레드 축소: 신용여건 개선(강도는 하이일드보다 약함)</t>
-  </si>
-  <si>
-    <t>마진부채(FINRA, 잔액)</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>투자자들이 증권사에서 빌려서 주식을 산 금액(레버리지 투자 규모)의 잔액</t>
-  </si>
-  <si>
-    <t>마진부채가 늘면 투자자들의 위험선호(레버리지 사용)가 커졌다는 뜻입니다. 반대로 주가 급락 시 마진콜(추가담보 요구)로 강제매도가 발생해 하락을 증폭시키는 '레버리지 청산' 리스크의 원천이 되기도 합니다.</t>
-  </si>
-  <si>
-    <t>레버리지 확대, 투자심리 과열 가능성(특히 사상최고치 경신 시 경계 신호로 해석되기도 함)</t>
-  </si>
-  <si>
-    <t>레버리지 축소, 급격한 하락은 강제청산(디레버리징) 진행 중일 가능성</t>
-  </si>
-  <si>
-    <t>미국 가계부채</t>
-  </si>
-  <si>
-    <t>CMDEBT</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CMDEBT</t>
-  </si>
-  <si>
-    <t>미국 가계 전체가 지고 있는 빚(주택담보대출, 신용카드 등)의 총액</t>
-  </si>
-  <si>
-    <t>가계부채가 소득 대비 과도하게 늘어나면 소비여력 축소, 금융위기 리스크로 이어질 수 있습니다(2008년 금융위기가 대표적 사례).</t>
-  </si>
-  <si>
-    <t>레버리지 확대, 장기적으로 소비여력·금융안정성에 부담 우려</t>
-  </si>
-  <si>
-    <t>디레버리징(부채 축소) 진행 중</t>
-  </si>
-  <si>
-    <t>미국 정부부채(총액)</t>
-  </si>
-  <si>
-    <t>GFDEBTN</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/GFDEBTN</t>
-  </si>
-  <si>
-    <t>미국 연방정부가 누적으로 지고 있는 빚의 총액</t>
-  </si>
-  <si>
-    <t>재정건전성과 장기 금리·인플레이션 우려에 영향을 줄 수 있는 구조적 지표입니다. 단기 주가 변동과의 직접적 상관은 약한 편입니다.</t>
-  </si>
-  <si>
-    <t>재정 부담 증가, 장기적으로 금리·인플레이션 상방 압력 우려</t>
-  </si>
-  <si>
-    <t>해당 없음(구조적으로 꾸준히 증가하는 지표라 감소는 매우 드묾)</t>
-  </si>
-  <si>
-    <t>외환·무역</t>
-  </si>
-  <si>
-    <t>미국 무역수지</t>
-  </si>
-  <si>
-    <t>BOPGSTB</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BOPGSTB</t>
-  </si>
-  <si>
-    <t>상품·서비스 수출액에서 수입액을 뺀 값(경상수지보다 좁은 개념)</t>
-  </si>
-  <si>
-    <t>무역정책, 관세 이슈 등에 민감하게 반응하며 매월 발표되어 경상수지보다 시장의 관심을 자주 받습니다.</t>
-  </si>
-  <si>
-    <t>적자 축소(또는 흑자 확대): 대외 경쟁력 개선 신호</t>
-  </si>
-  <si>
-    <t>적자 확대: 대외 경쟁력 약화 또는 내수 수요 강세 신호</t>
-  </si>
-  <si>
-    <t>미국 경상수지</t>
-  </si>
-  <si>
-    <t>IEABC</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/IEABC</t>
-  </si>
-  <si>
-    <t>상품·서비스·소득 등을 종합한 미국의 대외 거래 결과(적자/흑자)</t>
-  </si>
-  <si>
-    <t>미국은 구조적으로 경상수지 적자국입니다. 적자 확대는 달러 공급 증가로 이어져 장기적으로 달러 약세 요인이 될 수 있습니다.</t>
-  </si>
-  <si>
-    <t>적자 축소(또는 흑자 확대): 장기적으로 달러 강세 요인</t>
-  </si>
-  <si>
-    <t>적자 확대: 장기적으로 달러 약세 요인</t>
-  </si>
-  <si>
-    <t>원자재</t>
-  </si>
-  <si>
-    <t>WTI 원유</t>
-  </si>
-  <si>
-    <t>DCOILWTICO</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DCOILWTICO</t>
-  </si>
-  <si>
-    <t>미국산 원유의 대표 기준 가격</t>
-  </si>
-  <si>
-    <t>에너지비용, 인플레이션, 산유국 경기에 광범위한 영향을 미칩니다. 수요 견인형 상승은 경기 호조 반영, 공급 충격형 상승(전쟁·감산 등)은 인플레이션·소비위축 우려로 작용하는 등 원인에 따라 해석이 달라집니다.</t>
-  </si>
-  <si>
-    <t>수요 견인형: 경기 호조 반영, 주가에 우호적일 수 있음 / 공급 충격형: 인플레이션·소비위축 우려, 주가에 부담</t>
-  </si>
-  <si>
-    <t>수요 위축(경기 둔화 우려) 또는 공급 과잉을 반영</t>
-  </si>
-  <si>
-    <t>금 선물</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/GC=F</t>
-  </si>
-  <si>
-    <t>대표적인 안전자산이자 인플레이션 헤지 수단으로 여겨지는 금의 선물 가격</t>
-  </si>
-  <si>
-    <t>통상 금리(특히 실질금리)가 낮을수록, 지정학적·경제적 불확실성이 커질수록 매력이 높아지는 경향이 있습니다. 달러와는 대체로 반대 방향으로 움직입니다.</t>
-  </si>
-  <si>
-    <t>안전자산 선호 확대(불확실성 고조, 금리 하락, 달러 약세 국면)</t>
-  </si>
-  <si>
-    <t>위험자산 선호 확대(안정적 성장, 금리 상승, 달러 강세 국면)</t>
-  </si>
-  <si>
-    <t>은 선물</t>
-  </si>
-  <si>
-    <t>SI=F</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/SI=F</t>
-  </si>
-  <si>
-    <t>금과 유사한 안전자산 성격이지만, 전자·태양광 등 산업용 수요 비중이 높아 경기 민감도가 더 큰 귀금속</t>
-  </si>
-  <si>
-    <t>금보다 변동성이 크고, '안전자산' 성격과 '산업재' 성격이 혼재되어 있어 해석이 금보다 복잡합니다.</t>
-  </si>
-  <si>
-    <t>안전자산 수요 또는 산업용 수요(태양광 등 친환경 산업 확대) 증가</t>
-  </si>
-  <si>
-    <t>안전자산 수요 위축 또는 산업 경기 둔화</t>
-  </si>
-  <si>
-    <t>발틱운임지수(BDI) 프록시-건화물운임선물ETF</t>
-  </si>
-  <si>
-    <t>BDRY</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/quote/BDRY</t>
-  </si>
-  <si>
-    <t>벌크선 운임선물에 직접 투자하는 ETF(BDRY) 가격 — 발틱운임지수(BDI)와 가장 밀접하게 연동되는 무료 대안</t>
-  </si>
-  <si>
-    <t>발틱운임지수(BDI) 자체는 Baltic Exchange의 유료 데이터로만 제공되며 무료 API가 없습니다. 초기엔 해운주 ETF(SEA)를 프록시로 검토했으나, 이 ETF는 2022년경 펀드가 재편되며 그 이전 이력이 사라졌고 해운'주식'을 담아 BDI와 간접적 관계였습니다. 이후 Capesize·Panamax·Supramax 건화물 운임선물을 직접 편입하는 BDRY(2018년 3월 상장)로 교체해, BDI 실제 움직임에 훨씬 직접적으로 연동되도록 개선했습니다. 다만 운임선물 특성상 변동성이 매우 크고, 2018년 이전 이력은 없습니다.</t>
-  </si>
-  <si>
-    <t>글로벌 벌크화물(철광석·석탄·곡물 등) 물동량 확대, 교역 활발 신호</t>
-  </si>
-  <si>
-    <t>글로벌 벌크화물 물동량 위축, 교역 둔화 신호</t>
-  </si>
-  <si>
-    <t>밸류에이션 배수</t>
-  </si>
-  <si>
-    <t>S&amp;P500 PER(일반)</t>
-  </si>
-  <si>
-    <t>pe</t>
-  </si>
-  <si>
-    <t>multpl.com(Shiller 데이터 재정리)</t>
-  </si>
-  <si>
-    <t>https://www.multpl.com/</t>
-  </si>
-  <si>
-    <t>현재 주가를 최근 1년 실적(EPS)으로 나눈 값 - 가장 널리 쓰이는 밸류에이션 지표</t>
-  </si>
-  <si>
-    <t>CAPE보다 단기 실적 변동에 민감해서, 경기침체 직후 이익이 급감하면 오히려 PER이 비정상적으로 치솟는 왜곡이 나타날 수 있습니다.</t>
-  </si>
-  <si>
-    <t>고평가 신호(단, 이익 급감기에는 왜곡 가능성 있음)</t>
-  </si>
-  <si>
-    <t>저평가 신호</t>
-  </si>
-  <si>
-    <t>S&amp;P500 CAPE(실러PER)</t>
-  </si>
-  <si>
-    <t>cape</t>
-  </si>
-  <si>
-    <t>최근 10년치 물가조정 평균 실적으로 나눈 PER - 노벨경제학상 수상자 로버트 실러가 고안</t>
-  </si>
-  <si>
-    <t>10년 평균을 사용해 경기순환에 따른 일시적 실적 왜곡을 완화한 지표입니다. 역사적으로 CAPE가 높을수록 이후 10년간의 실질수익률이 낮게 나타나는 경향이 반복적으로 확인됐습니다. S&amp;P500 주가를 그대로 포함하는 지표라 S&amp;P500과의 상관계수 자체는 구조적으로 항상 높게 나오므로, 상관관계보다 '절대 수준'을 보는 것이 중요합니다.</t>
-  </si>
-  <si>
-    <t>고평가 신호(장기적으로 낮은 기대수익률과 연관되는 경향이 반복 확인됨)</t>
-  </si>
-  <si>
-    <t>저평가 신호(장기적으로 높은 기대수익률과 연관되는 경향이 반복 확인됨)</t>
-  </si>
-  <si>
-    <t>S&amp;P500 PBR(주가순자산)</t>
-  </si>
-  <si>
-    <t>price_to_book</t>
-  </si>
-  <si>
-    <t>주가를 기업의 순자산(장부가치)으로 나눈 값</t>
-  </si>
-  <si>
-    <t>자산 중심 산업(금융, 제조업)의 밸류에이션 평가에는 유용하나, 무형자산 비중이 큰 기술기업에는 왜곡이 있을 수 있습니다.</t>
-  </si>
-  <si>
-    <t>고평가 신호(단, 무형자산 비중이 큰 업종에는 왜곡 가능성)</t>
-  </si>
-  <si>
-    <t>저평가 신호(단, 무형자산 비중이 큰 업종에는 왜곡 가능성)</t>
-  </si>
-  <si>
-    <t>S&amp;P500 ROE(자기자본이익률, %)</t>
-  </si>
-  <si>
-    <t>roe</t>
-  </si>
-  <si>
-    <t>multpl(PBR÷PER), 자체 계산(정확한 항등식)</t>
-  </si>
-  <si>
-    <t>기업이 주주 자본(순자산) 대비 얼마나 효율적으로 이익을 내는지 보여주는 대표적 수익성 지표</t>
-  </si>
-  <si>
-    <t>ROE = 이익 ÷ 순자산. PBR(주가÷순자산)과 PER(주가÷이익)의 비율(PBR÷PER = 이익÷순자산)로 계산합니다. 같은 시점의 '주가'가 분자·분모에서 정확히 상쇄되므로 근사치가 아니라 수학적으로 정확한 값입니다.</t>
-  </si>
-  <si>
-    <t>자기자본 대비 수익성 개선</t>
-  </si>
-  <si>
-    <t>자기자본 대비 수익성 악화, 또는 자사주매입·배당으로 순자산이 줄어든 영향일 수도 있음</t>
-  </si>
-  <si>
-    <t>S&amp;P500 배당수익률(%)</t>
-  </si>
-  <si>
-    <t>dividend_yield</t>
-  </si>
-  <si>
-    <t>주가 대비 연간 배당금의 비율</t>
-  </si>
-  <si>
-    <t>채권금리와 비교해 주식의 상대적 매력을 가늠하는 전통적 지표입니다.</t>
-  </si>
-  <si>
-    <t>배당수익률 하락(주가 상승에 따른): 밸류에이션 부담 신호로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>배당수익률 상승(주가 하락에 따른): 상대적으로 매력적인 진입 구간으로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>S&amp;P500 이익수익률(%)</t>
-  </si>
-  <si>
-    <t>earnings_yield</t>
-  </si>
-  <si>
-    <t>PER의 역수(EPS/주가) - 주식을 채권처럼 봤을 때의 '수익률'</t>
-  </si>
-  <si>
-    <t>국채금리와 비교해 주식이 채권 대비 상대적으로 매력적인지 판단하는 데 쓰이는 지표입니다('Fed 모델'이라는 접근의 핵심 개념).</t>
-  </si>
-  <si>
-    <t>이익수익률이 국채금리보다 크게 낮으면: 채권 대비 주식 매력 저하 신호로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>이익수익률이 국채금리보다 크게 높으면: 채권 대비 주식 매력 상승 신호로 해석되는 경우가 많음</t>
-  </si>
-  <si>
-    <t>S&amp;P500 PEG비율(트레일링 근사)</t>
-  </si>
-  <si>
-    <t>peg</t>
-  </si>
-  <si>
-    <t>multpl(PER)+Yahoo Finance(가격) 조합, 자체 계산</t>
-  </si>
-  <si>
-    <t>https://www.multpl.com/s-p-500-pe-ratio</t>
-  </si>
-  <si>
-    <t>PER을 이익성장률로 나눠, '성장성 대비 얼마나 비싼가'를 보는 지표 (1.0 근처가 적정으로 통용됨)</t>
-  </si>
-  <si>
-    <t>PEG = PER ÷ 이익성장률(%). 전설적 투자자 피터 린치가 대중화한 지표로, 단순 PER만으로는 '성장이 빠른 기업(정당화되는 고PER)'과 '성장 없이 비싸기만 한 기업'을 구분 못 한다는 한계를 보완합니다. 정통 PEG는 애널리스트의 '향후' 이익성장률 전망치를 쓰지만, 이 전망치는 무료로 자동 수집할 수 있는 공개 소스가 없습니다(Yardeni·GuruFocus 등 유료). 이 대시보드의 PEG는 대신 실제 EPS의 '과거(trailing)' 12개월 성장률로 근사한 대체 지표이며, 미래 기대가 아닌 과거 실적 기준이라 전망치 기반 PEG보다 후행적입니다. 이익이 역성장(마이너스)한 구간은 PEG 정의상 의미가 없어 데이터에서 제외됩니다.</t>
-  </si>
-  <si>
-    <t>이익성장 대비 주가가 비싸지는 국면(단, 성장률 자체가 낮아져서 PEG가 오른 것인지 주가만 오른 것인지 구분 필요)</t>
-  </si>
-  <si>
-    <t>이익성장 대비 주가가 저렴해지는 국면(성장률이 빨라져서 낮아진 것이라면 오히려 긍정적 신호)</t>
-  </si>
-  <si>
-    <t>S&amp;P500 PSR(주가매출)</t>
-  </si>
-  <si>
-    <t>price_to_sales</t>
-  </si>
-  <si>
-    <t>주가를 기업의 매출로 나눈 값</t>
-  </si>
-  <si>
-    <t>아직 이익을 내지 못하는 성장기업(적자 스타트업 등) 밸류에이션을 평가할 때 특히 유용하게 쓰이는 지표입니다.</t>
-  </si>
-  <si>
-    <t>고평가 신호</t>
-  </si>
-  <si>
-    <t>S&amp;P500 배당성향(Payout Ratio, %)</t>
-  </si>
-  <si>
-    <t>payout</t>
-  </si>
-  <si>
-    <t>multpl(배당수익률×PER), 자체 계산(정확한 항등식)</t>
-  </si>
-  <si>
-    <t>기업이 번 이익 중 몇 %를 배당으로 나눠주는지 보여주는 지표</t>
-  </si>
-  <si>
-    <t>배당성향 = 배당 ÷ 이익. 배당수익률과 PER을 곱하면 주가가 상쇄되어 배당/이익이 정확히 산출됩니다. 최근 수십 년간 미국 기업들이 배당보다 자사주매입을 선호하는 추세로 바뀌면서 이 비율 자체가 구조적으로 낮아져 왔다는 점을 감안해서 봐야 합니다.</t>
-  </si>
-  <si>
-    <t>이익 중 더 많은 몫을 배당으로 지급</t>
-  </si>
-  <si>
-    <t>이익 대비 배당 지급 비중 축소(재투자 확대 또는 자사주매입 선호)</t>
-  </si>
-  <si>
-    <t>미국 기업이익률(GDP대비, %)</t>
-  </si>
-  <si>
-    <t>CP/GDP</t>
-  </si>
-  <si>
-    <t>FRED(CP÷GDP), 자체 계산</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/CP</t>
-  </si>
-  <si>
-    <t>미국 전체 기업이 벌어들인 이익이 국가경제(GDP) 전체에서 차지하는 비중</t>
-  </si>
-  <si>
-    <t>FRED 공식 기업이익(CP) ÷ 명목GDP로 계산됩니다. '지금 기업 마진이 역사적으로 높은 수준인지'를 가늠할 수 있는 대표적인 무료 매크로 프록시입니다.</t>
-  </si>
-  <si>
-    <t>기업 부문이 경제 전체에서 더 많은 몫을 가져가는 국면</t>
-  </si>
-  <si>
-    <t>기업이익 비중 축소</t>
-  </si>
-  <si>
-    <t>복합·추세지표</t>
-  </si>
-  <si>
-    <t>버핏지수(시총/GDP, %)</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
-    <t>FRED(시가총액) + FRED(GDP), 자체 계산</t>
-  </si>
-  <si>
-    <t>미국 전체 상장주식 시가총액을 GDP로 나눈 값 - 워런 버핏이 '최고의 단일 밸류에이션 지표'라 언급했던 지표</t>
-  </si>
-  <si>
-    <t>100%를 넘으면 주식시장 규모가 실물경제보다 커졌다는 뜻으로, 역사적으로 높을수록 이후 장기수익률이 낮게 나타나는 경향이 있습니다. 다만 저금리 시대, 미국 기업의 해외매출 비중 증가 등 구조적 요인으로 '정상' 기준선 자체가 과거보다 높아졌다는 지적도 있어, 절대 기준보다는 참고 지표로 활용하는 것이 안전합니다.</t>
-  </si>
-  <si>
-    <t>고평가 신호(장기적으로 낮은 기대수익률과 연관되는 경향)</t>
-  </si>
-  <si>
-    <t>저평가 신호(장기적으로 높은 기대수익률과 연관되는 경향)</t>
-  </si>
-  <si>
-    <t>S&amp;P500 추세이격률(%)</t>
-  </si>
-  <si>
-    <t>S&amp;P500이 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
-  </si>
-  <si>
-    <t>지수의 절대 레벨이 아니라, '역사적 추세 대비 지금이 과열·침체 국면인지'를 판단하는 용도로 쓰입니다.</t>
-  </si>
-  <si>
-    <t>버핏지수 추세이격률(%)</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>버핏지수 기반 자체 계산(추세선 대비 이격도)</t>
-  </si>
-  <si>
-    <t>버핏지수가 자기 자신의 장기 추세선 대비 몇 % 위/아래에 있는지</t>
-  </si>
-  <si>
-    <t>절대수준(100%, 200% 등)보다 '추세 대비 이례적인 수준인지'를 보는 보조지표입니다.</t>
-  </si>
-  <si>
-    <t>양수: 추세선 위(고평가 국면)</t>
-  </si>
-  <si>
-    <t>음수: 추세선 아래(저평가 국면)</t>
-  </si>
-  <si>
-    <t>S&amp;P500 CAPE 추세이격률(%)</t>
-  </si>
-  <si>
-    <t>CAPE(실러PER) 자체가 CAPE의 장기 추세선 대비 몇 % 위/아래에 있는지</t>
-  </si>
-  <si>
-    <t>밸류에이션 지표(CAPE)의 '밸류에이션'을 다시 보는 2차 지표로, CAPE 절대수준만으로는 놓치기 쉬운 '추세 이탈 정도'를 보완합니다.</t>
-  </si>
-  <si>
-    <t>양수: CAPE 추세선 위(밸류에이션이 자기 역사보다도 더 이례적으로 높음)</t>
-  </si>
-  <si>
-    <t>음수: CAPE 추세선 아래</t>
-  </si>
-  <si>
-    <t>나스닥100 추세이격률(%)</t>
-  </si>
-  <si>
-    <t>나스닥100이 자기 자신의 장기 로그추세선 대비 몇 % 위/아래에 있는지</t>
-  </si>
-  <si>
-    <t>S&amp;P500 추세이격률과 같은 개념을 나스닥100에 적용한 지표로, 기술주 특유의 과열/침체 국면 판단에 활용됩니다.</t>
-  </si>
-  <si>
-    <t>S&amp;P500 월간수익률(%)</t>
-  </si>
-  <si>
-    <t>S&amp;P500의 전월 대비 등락률</t>
-  </si>
-  <si>
-    <t>절대 가격(추세형) 지표가 아닌 '변화율(정체형)' 지표라, GDP성장률처럼 이미 변화율인 지표와 짝지어 비교할 때 허위상관(추세 혼입)을 피할 수 있어 유용합니다.</t>
-  </si>
-  <si>
-    <t>나스닥100 월간수익률(%)</t>
-  </si>
-  <si>
-    <t>나스닥100의 전월 대비 등락률</t>
-  </si>
-  <si>
-    <t>S&amp;P500 월간수익률과 같은 용도로, 기술주 지수의 변화율만 따로 비교하고 싶을 때 사용합니다.</t>
-  </si>
-  <si>
-    <t>지표 개수</t>
-  </si>
-  <si>
-    <t>합계</t>
-  </si>
-  <si>
-    <t>변경사항</t>
-  </si>
-  <si>
-    <t>① 신규 카테고리 '한국 주요지표' 추가 (15개 지표) — 기존 8개 카테고리 → 9개로 확장</t>
-  </si>
-  <si>
-    <t>② 한국 CPI, 한국 명목GDP, 한국 기준금리, 한국 M2 통화량, 한국 무역수지, 한국 경상수지 신규 추가</t>
-  </si>
-  <si>
-    <t>③ 코스피 → 코스피지수, 코스닥 → 코스닥지수로 이름 변경 및 '지수·주가'에서 '한국 주요지표'로 이동</t>
-  </si>
-  <si>
-    <t>④ 코스피 시가총액, KOSPI PER, KOSPI PBR, KOSPI 배당수익률 신규 추가 (KOSIS 연동)</t>
-  </si>
-  <si>
-    <t>⑤ 코스피 추세이격률(%), 코스피 월간수익률(%)을 '복합·추세지표'에서 '한국 주요지표'로 이동</t>
-  </si>
-  <si>
-    <t>⑥ 한국 기준금리·M2는 ECOS(한국은행), KOSPI PER/PBR/배당수익률/시가총액은 KOSIS(국가통계포털) API 신규 연동</t>
-  </si>
-  <si>
-    <t>⑦ '밸류에이션(복합지표)' 카테고리를 '밸류에이션 배수'와 '복합·추세지표'로 분리</t>
-  </si>
-  <si>
-    <t>⑧ S&amp;P500 ROE, 배당성향(Payout Ratio), 미국 기업이익률(GDP대비) 신규 추가</t>
-  </si>
-  <si>
-    <t>⑨ 미국 거시지표: 명목GDP를 CPI 이전으로, 비농업고용자수를 실업률 다음으로 순서 변경</t>
-  </si>
-  <si>
-    <t>⑩ 지수·주가: 코스피/코스닥 제거 후 지수→시가총액→VIX→CBOE 순으로 재배열</t>
-  </si>
-  <si>
-    <t>⑪ 각 카테고리 내부는 주가 관련성·시장 주목도가 높은 지표 순으로 재배열</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">코스피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시가총액</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">코스피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추세이격률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(%)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">코스피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>월간수익률</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(%)</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1824,6 +1881,17 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1921,7 +1989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1979,6 +2047,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2355,68 +2426,68 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="38.25">
+    <row r="4" spans="1:10" ht="25.5">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
+      <c r="B4" s="29" t="s">
+        <v>577</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>22</v>
+      <c r="B5" s="29" t="s">
+        <v>578</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="38.25">
@@ -2424,127 +2495,127 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>579</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="38.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="25.5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="38.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="25.5">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="25.5">
@@ -2552,31 +2623,29 @@
         <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>580</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="25.5">
@@ -2584,31 +2653,29 @@
         <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>71</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="25.5">
@@ -2616,31 +2683,31 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="38.25">
@@ -2648,63 +2715,63 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="25.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="38.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="38.25">
@@ -2712,31 +2779,31 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="25.5">
@@ -2744,61 +2811,63 @@
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="25.5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="38.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="F17" s="3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="25.5">
@@ -2806,2129 +2875,2131 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="F18" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="38.25">
       <c r="A19" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="25.5">
       <c r="A20" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="38.25">
       <c r="A21" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="38.25">
       <c r="A22" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="51">
       <c r="A23" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="38.25">
       <c r="A24" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="38.25">
       <c r="A25" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="25.5">
       <c r="A26" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="25.5">
       <c r="A27" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="25.5">
       <c r="A28" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="25.5">
       <c r="A29" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="25.5">
       <c r="A30" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="25.5">
       <c r="A31" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="38.25">
       <c r="A32" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="25.5">
       <c r="A33" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="25.5">
       <c r="A34" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="25.5">
       <c r="A35" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="25.5">
       <c r="A36" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="25.5">
       <c r="A37" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="38.25">
       <c r="A38" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="38.25">
       <c r="A39" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="38.25">
       <c r="A40" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="38.25">
       <c r="A41" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="63.75">
       <c r="A42" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="25.5">
       <c r="A43" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="38.25">
       <c r="A44" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="25.5">
       <c r="A45" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="J45" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="25.5">
       <c r="A46" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="25.5">
       <c r="A47" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="25.5">
       <c r="A48" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="25.5">
       <c r="A49" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="25.5">
       <c r="A50" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="25.5">
       <c r="A51" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="25.5">
       <c r="A52" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="63.75">
       <c r="A53" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="25.5">
       <c r="A54" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="25.5">
       <c r="A55" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="25.5">
       <c r="A56" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="25.5">
       <c r="A57" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="25.5">
       <c r="A58" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="38.25">
       <c r="A59" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="25.5">
       <c r="A60" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="25.5">
       <c r="A61" s="8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="25.5">
       <c r="A62" s="9" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="25.5">
       <c r="A63" s="9" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="38.25">
       <c r="A64" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="25.5">
       <c r="A65" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="25.5">
       <c r="A66" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="89.25">
       <c r="A67" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="25.5">
       <c r="A68" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="63.75">
       <c r="A69" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="25.5">
       <c r="A70" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="38.25">
       <c r="A71" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="38.25">
       <c r="A72" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="38.25">
       <c r="A73" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="102">
       <c r="A74" s="11" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="25.5">
       <c r="A75" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="51">
       <c r="A76" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="25.5">
       <c r="A77" s="11" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="51">
       <c r="A78" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="25.5">
       <c r="A79" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="25.5">
       <c r="A80" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="25.5">
       <c r="A81" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="25.5">
       <c r="A82" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="25.5">
       <c r="A83" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="25.5">
       <c r="A84" s="12" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4956,7 +5027,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4969,7 +5040,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B3" s="15">
         <v>19</v>
@@ -4977,7 +5048,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="17" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B4" s="15">
         <v>11</v>
@@ -4985,7 +5056,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="18" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B5" s="15">
         <v>7</v>
@@ -4993,7 +5064,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="19" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B6" s="15">
         <v>6</v>
@@ -5001,7 +5072,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="20" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B7" s="15">
         <v>2</v>
@@ -5009,7 +5080,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="21" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B8" s="15">
         <v>4</v>
@@ -5017,7 +5088,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="22" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B9" s="15">
         <v>10</v>
@@ -5025,7 +5096,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="23" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B10" s="15">
         <v>7</v>
@@ -5033,7 +5104,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="24" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B11" s="24">
         <v>81</v>
@@ -5055,62 +5126,62 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="13" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="25" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="25" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="25" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="25" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="25" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="25" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="25" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="25" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="25" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="25" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="25" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
